--- a/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_39.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.1/Output_18_39.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3694052.091294374</v>
+        <v>3694135.847615198</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4036467.593299042</v>
+        <v>4036467.593299041</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4036467.593299042</v>
+        <v>4036467.593299041</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>48818732.47780246</v>
+        <v>48818732.47780245</v>
       </c>
     </row>
   </sheetData>
@@ -654,22 +654,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>60.20483817079537</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2.969432588523773</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -708,19 +708,19 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
         <v>124</v>
-      </c>
-      <c r="V2" t="n">
-        <v>124</v>
-      </c>
-      <c r="W2" t="n">
-        <v>121.9017673171935</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>111.3174326828064</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>111.535425392244</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,10 +784,10 @@
         <v>121.0985520093604</v>
       </c>
       <c r="S3" t="n">
-        <v>124</v>
+        <v>58.73324524763018</v>
       </c>
       <c r="T3" t="n">
-        <v>49.92715283852002</v>
+        <v>3.658482198645913</v>
       </c>
       <c r="U3" t="n">
         <v>0.182623911130122</v>
@@ -848,19 +848,19 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>117.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>124</v>
+        <v>109.2191999999999</v>
       </c>
       <c r="P4" t="n">
         <v>124</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="R4" t="n">
-        <v>116.1204853840528</v>
+        <v>124</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2.969432588523748</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -942,25 +942,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>76.89299192292594</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>124</v>
       </c>
       <c r="X5" t="n">
-        <v>96.9968490965957</v>
+        <v>76.67030669884335</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="6">
@@ -1015,22 +1015,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>121.0985520093604</v>
       </c>
       <c r="S6" t="n">
-        <v>58.73324524763017</v>
+        <v>59.7021417242934</v>
       </c>
       <c r="T6" t="n">
-        <v>3.658482198645892</v>
+        <v>124</v>
       </c>
       <c r="U6" t="n">
-        <v>111.7180493033741</v>
+        <v>0.182623911130122</v>
       </c>
       <c r="V6" t="n">
-        <v>14.51066719152016</v>
+        <v>124</v>
       </c>
       <c r="W6" t="n">
         <v>32.37314290982852</v>
@@ -1082,19 +1082,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>65.22787369763185</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>117.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>109.2191999999999</v>
+      </c>
+      <c r="P7" t="n">
         <v>124</v>
       </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
       <c r="Q7" t="n">
-        <v>50.89261168642094</v>
+        <v>124</v>
       </c>
       <c r="R7" t="n">
         <v>124</v>
@@ -1128,19 +1128,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>78.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>15.02138475155925</v>
+        <v>46.47457824299391</v>
       </c>
       <c r="D8" t="n">
         <v>7.339155739849787</v>
       </c>
       <c r="E8" t="n">
-        <v>1.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.889628708011855</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>34.90777784081023</v>
       </c>
       <c r="T8" t="n">
         <v>180.2263756984131</v>
@@ -1188,16 +1188,16 @@
         <v>246.1582613727313</v>
       </c>
       <c r="V8" t="n">
-        <v>226.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>235.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>189.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>108.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1210,17 +1210,17 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>203.5379577516481</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>263</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,10 +1255,10 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R9" t="n">
-        <v>263</v>
+        <v>118.0985520093604</v>
       </c>
       <c r="S9" t="n">
-        <v>263</v>
+        <v>55.73324524763017</v>
       </c>
       <c r="T9" t="n">
         <v>0.6584821986458915</v>
@@ -1267,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>65.4917137518849</v>
+        <v>11.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>29.37314290982852</v>
@@ -1322,7 +1322,7 @@
         <v>62.22787369763186</v>
       </c>
       <c r="N10" t="n">
-        <v>114.0987146159472</v>
+        <v>3.23385178032159</v>
       </c>
       <c r="O10" t="n">
         <v>187.4880558822936</v>
@@ -1334,7 +1334,7 @@
         <v>263</v>
       </c>
       <c r="R10" t="n">
-        <v>152.1351371643744</v>
+        <v>263</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1371,7 +1371,7 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1416,25 +1416,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>168.8929919229259</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>275.2263756984131</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>324.0000000000135</v>
       </c>
       <c r="V11" t="n">
         <v>321.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>104.7878190113195</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>284.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>52.01996667408179</v>
       </c>
     </row>
     <row r="12">
@@ -1459,10 +1459,10 @@
         <v>31.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>17.31795096936696</v>
+        <v>17.31795096936697</v>
       </c>
       <c r="H12" t="n">
-        <v>20.09646454491173</v>
+        <v>20.0964645449117</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1498,10 +1498,10 @@
         <v>150.7332452476302</v>
       </c>
       <c r="T12" t="n">
-        <v>95.65848219864591</v>
+        <v>95.65848219864588</v>
       </c>
       <c r="U12" t="n">
-        <v>92.18262391113012</v>
+        <v>92.18262391113015</v>
       </c>
       <c r="V12" t="n">
         <v>106.5106671915202</v>
@@ -1553,28 +1553,28 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>63.00034946925456</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>157.2278736976319</v>
+        <v>117.7924295017591</v>
       </c>
       <c r="N13" t="n">
         <v>209.0987146159472</v>
       </c>
       <c r="O13" t="n">
-        <v>282.4880558822937</v>
+        <v>282.4880558822936</v>
       </c>
       <c r="P13" t="n">
-        <v>173.3502676156238</v>
+        <v>324</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="R13" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>48.21393871924886</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>141.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E14" t="n">
         <v>96.36328960686865</v>
@@ -1620,7 +1620,7 @@
         <v>94.96943258852374</v>
       </c>
       <c r="H14" t="n">
-        <v>91.94017126634148</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1653,10 +1653,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>168.8929919229259</v>
       </c>
       <c r="T14" t="n">
-        <v>89.89107542043635</v>
+        <v>234.599099024002</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>321.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>213.0985520093604</v>
+        <v>211.3499952661064</v>
       </c>
       <c r="S15" t="n">
         <v>150.7332452476302</v>
@@ -1744,7 +1744,7 @@
         <v>106.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>122.6245861665787</v>
+        <v>124.3731429098285</v>
       </c>
       <c r="X15" t="n">
         <v>111.8627394453875</v>
@@ -1796,22 +1796,22 @@
         <v>157.2278736976318</v>
       </c>
       <c r="N16" t="n">
-        <v>209.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>282.4880558822936</v>
       </c>
       <c r="P16" t="n">
-        <v>180.0522622171663</v>
+        <v>324</v>
       </c>
       <c r="Q16" t="n">
         <v>324</v>
       </c>
       <c r="R16" t="n">
-        <v>324</v>
+        <v>58.44898223157098</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>48.21393871924888</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1839,13 +1839,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>86.99931295557451</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>54.47457824299391</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>15.33915573984979</v>
       </c>
       <c r="E17" t="n">
         <v>9.363289606868648</v>
@@ -1899,16 +1899,16 @@
         <v>254.1582613727313</v>
       </c>
       <c r="V17" t="n">
-        <v>234.8510241668239</v>
+        <v>230.5267357542916</v>
       </c>
       <c r="W17" t="n">
-        <v>243.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>197.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>25.43271522774474</v>
+        <v>116.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1921,17 +1921,17 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>319.5683543203628</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>324</v>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>202.6112915517259</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>248.2382386891274</v>
+        <v>126.0985520093604</v>
       </c>
       <c r="S18" t="n">
         <v>63.73324524763018</v>
@@ -1975,7 +1975,7 @@
         <v>8.658482198645913</v>
       </c>
       <c r="U18" t="n">
-        <v>324</v>
+        <v>5.182623911130122</v>
       </c>
       <c r="V18" t="n">
         <v>19.51066719152016</v>
@@ -2076,25 +2076,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.70368788815486</v>
+        <v>86.99931295557451</v>
       </c>
       <c r="C20" t="n">
         <v>54.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15.33915573984979</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>9.363289606868648</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>9.889628708011855</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>7.969432588523773</v>
       </c>
       <c r="H20" t="n">
-        <v>4.940171266341508</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>81.89299192292594</v>
+        <v>51.94043225645508</v>
       </c>
       <c r="T20" t="n">
         <v>188.2263756984131</v>
@@ -2142,10 +2142,10 @@
         <v>243.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>197.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>116.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2161,16 +2161,16 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1.77360335099477</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>325.317950969367</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2200,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>126.0985520093604</v>
@@ -2212,16 +2212,16 @@
         <v>8.658482198645913</v>
       </c>
       <c r="U21" t="n">
-        <v>328</v>
+        <v>5.182623911130122</v>
       </c>
       <c r="V21" t="n">
         <v>19.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>328</v>
+        <v>37.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>275.2457388924556</v>
+        <v>24.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>4.391392766134345</v>
@@ -2334,7 +2334,7 @@
         <v>7.940171266341508</v>
       </c>
       <c r="I23" t="n">
-        <v>1.362235606519822</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.362235606519632</v>
       </c>
       <c r="S23" t="n">
         <v>84.89299192292594</v>
@@ -2392,19 +2392,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>182.9186577552279</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2455,13 +2455,13 @@
         <v>22.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>127.6990727953849</v>
+        <v>40.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>399.0000000000007</v>
+        <v>27.86273944538755</v>
       </c>
       <c r="Y24" t="n">
-        <v>399.0000000000007</v>
+        <v>7.391392766134345</v>
       </c>
     </row>
     <row r="25">
@@ -2556,10 +2556,10 @@
         <v>142.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>103.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F26" t="n">
         <v>97.88962870801186</v>
@@ -2601,13 +2601,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>169.8929919229259</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>225.0967470931289</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>322.8510241668239</v>
@@ -2616,10 +2616,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>285.2818334606677</v>
+        <v>142.1440220810456</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>204.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -2741,22 +2741,22 @@
         <v>64.00034946925459</v>
       </c>
       <c r="M28" t="n">
-        <v>158.2278736976318</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>210.0987146159472</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>283.4880558822936</v>
+        <v>174.2635768156934</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>328.0000000000136</v>
       </c>
       <c r="Q28" t="n">
-        <v>328.0000000000127</v>
+        <v>328.0000000000123</v>
       </c>
       <c r="R28" t="n">
-        <v>178.4489326198426</v>
+        <v>328.0000000000087</v>
       </c>
       <c r="S28" t="n">
         <v>49.21393871924888</v>
@@ -2790,22 +2790,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>26.20169782927421</v>
       </c>
       <c r="D29" t="n">
         <v>103.3391557398498</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>97.36328960686865</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>97.88962870801186</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>92.94017126634148</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2844,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>29.1129539498334</v>
+        <v>328.0000000000237</v>
       </c>
       <c r="V29" t="n">
         <v>322.8510241668239</v>
       </c>
       <c r="W29" t="n">
-        <v>328.0000000000186</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>285.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
         <v>204.3174326828064</v>
@@ -2914,7 +2914,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>214.0985520093604</v>
+        <v>212.8731952661176</v>
       </c>
       <c r="S30" t="n">
         <v>151.7332452476302</v>
@@ -2929,7 +2929,7 @@
         <v>107.5106671915202</v>
       </c>
       <c r="W30" t="n">
-        <v>124.1477861665745</v>
+        <v>125.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>112.8627394453875</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>64.00034946925459</v>
       </c>
       <c r="M31" t="n">
         <v>158.2278736976318</v>
@@ -2984,16 +2984,16 @@
         <v>210.0987146159472</v>
       </c>
       <c r="O31" t="n">
-        <v>283.4880558822936</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>328.0000000000265</v>
+        <v>328.000000000027</v>
       </c>
       <c r="Q31" t="n">
-        <v>291.6632208083323</v>
+        <v>328.0000000000291</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>183.1509272213416</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3078,7 +3078,7 @@
         <v>11.89299192292594</v>
       </c>
       <c r="T32" t="n">
-        <v>12.47766745752263</v>
+        <v>118.2263756984131</v>
       </c>
       <c r="U32" t="n">
         <v>184.1582613727313</v>
@@ -3087,7 +3087,7 @@
         <v>164.8510241668239</v>
       </c>
       <c r="W32" t="n">
-        <v>173.3734759809475</v>
+        <v>67.62476774005704</v>
       </c>
       <c r="X32" t="n">
         <v>127.2818334606677</v>
@@ -3109,22 +3109,22 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="F33" t="n">
-        <v>111.2534479906303</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>190.000000000003</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R33" t="n">
         <v>56.09855200936045</v>
@@ -3166,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>181.9891262963802</v>
       </c>
       <c r="X33" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2278736976318783</v>
+        <v>0.06461086188733248</v>
       </c>
       <c r="N34" t="n">
         <v>52.09871461594719</v>
@@ -3227,10 +3227,10 @@
         <v>179.7006186397529</v>
       </c>
       <c r="Q34" t="n">
-        <v>189.8367371643189</v>
+        <v>190.0000000000598</v>
       </c>
       <c r="R34" t="n">
-        <v>190.0000000000555</v>
+        <v>190.0000000000591</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -3312,22 +3312,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>11.89299192292594</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>67.30576731697234</v>
       </c>
       <c r="U35" t="n">
-        <v>129.0000000000726</v>
+        <v>129.0000000000799</v>
       </c>
       <c r="V35" t="n">
-        <v>40.13162897789184</v>
+        <v>129.0000000000731</v>
       </c>
       <c r="W35" t="n">
-        <v>129.0000000000609</v>
+        <v>129.0000000000682</v>
       </c>
       <c r="X35" t="n">
-        <v>127.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
         <v>46.31743268280638</v>
@@ -3343,64 +3343,64 @@
         <v>0</v>
       </c>
       <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>113.6231999999835</v>
+      </c>
+      <c r="F36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>56.09855200936045</v>
-      </c>
       <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
       <c r="V36" t="n">
-        <v>57.52464799062305</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
         <v>0</v>
@@ -3461,13 +3461,13 @@
         <v>125.4880558822937</v>
       </c>
       <c r="P37" t="n">
-        <v>129.0000000000772</v>
+        <v>129.0000000000881</v>
       </c>
       <c r="Q37" t="n">
-        <v>129.0000000000732</v>
+        <v>65.0364295015894</v>
       </c>
       <c r="R37" t="n">
-        <v>65.03642950160874</v>
+        <v>129.0000000000816</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>16.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -3549,25 +3549,25 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>11.89299192292592</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>118.2263756984131</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>50.90525327953878</v>
+        <v>129.0000000001094</v>
       </c>
       <c r="V38" t="n">
-        <v>129.0000000000736</v>
+        <v>115.3413665391294</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>129.0000000000935</v>
       </c>
       <c r="X38" t="n">
         <v>127.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>46.31743268280638</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -3580,10 +3580,10 @@
         <v>129.0000000000091</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="D39" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -3643,10 +3643,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>129.0000000000091</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3689,7 +3689,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.2278736976318569</v>
       </c>
       <c r="N40" t="n">
         <v>52.09871461594719</v>
@@ -3698,13 +3698,13 @@
         <v>125.4880558822936</v>
       </c>
       <c r="P40" t="n">
-        <v>129.0000000001102</v>
+        <v>129.0000000001175</v>
       </c>
       <c r="Q40" t="n">
-        <v>129.0000000001064</v>
+        <v>64.80855580390612</v>
       </c>
       <c r="R40" t="n">
-        <v>65.03642950154259</v>
+        <v>129.0000000001037</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>113.6231999996445</v>
+        <v>129.0000000000164</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>129.0000000000164</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>129.0000000001712</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>129.0000000001678</v>
+        <v>129.0000000001821</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>113.6231999997851</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -3820,19 +3820,19 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>102.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>94.63624233787687</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>83.0964645449117</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,25 +3862,25 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>129.0000000001741</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>113.6231999995424</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>90.95280621932818</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>129.0000000001806</v>
       </c>
       <c r="V42" t="n">
-        <v>129.0000000001417</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>129.0000000001417</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
         <v>0</v>
@@ -3893,10 +3893,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>27.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>40.53621805555548</v>
@@ -3905,7 +3905,7 @@
         <v>35.98090483695654</v>
       </c>
       <c r="F43" t="n">
-        <v>29.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3920,16 +3920,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>2.457167243766001</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>126.0003494692546</v>
       </c>
       <c r="M43" t="n">
-        <v>79.94930531771985</v>
+        <v>129.0000000001924</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>82.75096304372288</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>111.2139387192489</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3959,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.443645430107551</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3978,19 +3978,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>125.000000000035</v>
       </c>
       <c r="F44" t="n">
-        <v>125.0000000000355</v>
+        <v>125.000000000035</v>
       </c>
       <c r="G44" t="n">
-        <v>110.0999999998934</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>125.0000000000355</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4026,7 +4026,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>125.000000000035</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4035,7 +4035,7 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>110.0999999998948</v>
       </c>
       <c r="X44" t="n">
         <v>0</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>125.000000000303</v>
+        <v>125.0000000003158</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4066,7 +4066,7 @@
         <v>94.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>80.31795096936696</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -4099,19 +4099,19 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>125.0000000003838</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>125.0000000003348</v>
+        <v>60.14580669205657</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>125.0000000003035</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>15.4637576611818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4130,10 +4130,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>42.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C46" t="n">
-        <v>27.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>40.53621805555548</v>
@@ -4157,25 +4157,25 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>2.457167243766008</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>54.44805654541189</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
         <v>125</v>
       </c>
-      <c r="M46" t="n">
-        <v>64.68648946706016</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -4199,7 +4199,7 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>42.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4297,19 +4297,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.92</v>
+        <v>72.24013045090727</v>
       </c>
       <c r="C2" t="n">
-        <v>9.92</v>
+        <v>22.26580899333765</v>
       </c>
       <c r="D2" t="n">
-        <v>9.92</v>
+        <v>22.26580899333765</v>
       </c>
       <c r="E2" t="n">
-        <v>9.92</v>
+        <v>17.85844575407639</v>
       </c>
       <c r="F2" t="n">
-        <v>9.92</v>
+        <v>12.91942685709472</v>
       </c>
       <c r="G2" t="n">
         <v>9.92</v>
@@ -4324,22 +4324,22 @@
         <v>41.43406683243596</v>
       </c>
       <c r="K2" t="n">
-        <v>164.1940668324359</v>
+        <v>140.6606624103254</v>
       </c>
       <c r="L2" t="n">
-        <v>286.954066832436</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="M2" t="n">
-        <v>322.2245487608371</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="N2" t="n">
-        <v>322.2245487608371</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="O2" t="n">
-        <v>384.1105430081138</v>
+        <v>325.3066566576019</v>
       </c>
       <c r="P2" t="n">
-        <v>496</v>
+        <v>437.1961136494882</v>
       </c>
       <c r="Q2" t="n">
         <v>496</v>
@@ -4351,22 +4351,22 @@
         <v>496</v>
       </c>
       <c r="T2" t="n">
-        <v>496</v>
+        <v>370.7474747474747</v>
       </c>
       <c r="U2" t="n">
         <v>370.7474747474747</v>
       </c>
       <c r="V2" t="n">
+        <v>370.7474747474747</v>
+      </c>
+      <c r="W2" t="n">
+        <v>370.7474747474747</v>
+      </c>
+      <c r="X2" t="n">
         <v>245.4949494949495</v>
       </c>
-      <c r="W2" t="n">
-        <v>122.3618511947539</v>
-      </c>
-      <c r="X2" t="n">
-        <v>122.3618511947539</v>
-      </c>
       <c r="Y2" t="n">
-        <v>9.92</v>
+        <v>133.0530983001955</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="C3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="D3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="E3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="F3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="G3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="H3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="I3" t="n">
         <v>9.92</v>
@@ -4406,13 +4406,13 @@
         <v>132.68</v>
       </c>
       <c r="L3" t="n">
-        <v>132.68</v>
+        <v>255.44</v>
       </c>
       <c r="M3" t="n">
-        <v>250.48</v>
+        <v>255.44</v>
       </c>
       <c r="N3" t="n">
-        <v>250.48</v>
+        <v>255.44</v>
       </c>
       <c r="O3" t="n">
         <v>373.24</v>
@@ -4427,25 +4427,25 @@
         <v>253.2092184811983</v>
       </c>
       <c r="S3" t="n">
-        <v>127.9566932286731</v>
+        <v>193.8827081300568</v>
       </c>
       <c r="T3" t="n">
-        <v>77.5252257150165</v>
+        <v>190.187271565768</v>
       </c>
       <c r="U3" t="n">
-        <v>77.34075711791537</v>
+        <v>190.0028029686668</v>
       </c>
       <c r="V3" t="n">
-        <v>62.68351753052128</v>
+        <v>175.3455633812727</v>
       </c>
       <c r="W3" t="n">
-        <v>29.98337317715914</v>
+        <v>142.6454190279106</v>
       </c>
       <c r="X3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
       <c r="Y3" t="n">
-        <v>9.92</v>
+        <v>122.5820458507515</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165.0255383342358</v>
+        <v>298.7882006679436</v>
       </c>
       <c r="C4" t="n">
-        <v>165.0255383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="D4" t="n">
-        <v>165.0255383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="E4" t="n">
-        <v>165.0255383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="F4" t="n">
-        <v>165.0255383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="G4" t="n">
-        <v>287.7855383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="H4" t="n">
-        <v>287.7855383342358</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="I4" t="n">
-        <v>410.5455383342357</v>
+        <v>421.5482006679436</v>
       </c>
       <c r="J4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="K4" t="n">
-        <v>467.290345974562</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
         <v>496</v>
@@ -4491,16 +4491,16 @@
         <v>496</v>
       </c>
       <c r="N4" t="n">
-        <v>377.7184700849018</v>
+        <v>496</v>
       </c>
       <c r="O4" t="n">
-        <v>252.4659448323766</v>
+        <v>385.6775757575758</v>
       </c>
       <c r="P4" t="n">
-        <v>127.2134195798513</v>
+        <v>260.4250505050505</v>
       </c>
       <c r="Q4" t="n">
-        <v>127.2134195798513</v>
+        <v>135.1725252525252</v>
       </c>
       <c r="R4" t="n">
         <v>9.92</v>
@@ -4518,13 +4518,13 @@
         <v>53.26820066794363</v>
       </c>
       <c r="W4" t="n">
-        <v>53.26820066794363</v>
+        <v>176.0282006679436</v>
       </c>
       <c r="X4" t="n">
-        <v>53.26820066794363</v>
+        <v>298.7882006679436</v>
       </c>
       <c r="Y4" t="n">
-        <v>53.26820066794363</v>
+        <v>298.7882006679436</v>
       </c>
     </row>
     <row r="5">
@@ -4534,19 +4534,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.26580899333763</v>
+        <v>20.36359165641393</v>
       </c>
       <c r="C5" t="n">
-        <v>22.26580899333763</v>
+        <v>20.36359165641393</v>
       </c>
       <c r="D5" t="n">
-        <v>22.26580899333763</v>
+        <v>9.92</v>
       </c>
       <c r="E5" t="n">
-        <v>17.85844575407637</v>
+        <v>9.92</v>
       </c>
       <c r="F5" t="n">
-        <v>12.9194268570947</v>
+        <v>9.92</v>
       </c>
       <c r="G5" t="n">
         <v>9.92</v>
@@ -4567,7 +4567,7 @@
         <v>263.4206624103253</v>
       </c>
       <c r="M5" t="n">
-        <v>322.2245487608371</v>
+        <v>263.4206624103253</v>
       </c>
       <c r="N5" t="n">
         <v>322.2245487608371</v>
@@ -4585,25 +4585,25 @@
         <v>496</v>
       </c>
       <c r="S5" t="n">
-        <v>496</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="T5" t="n">
-        <v>496</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="U5" t="n">
-        <v>370.7474747474747</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="V5" t="n">
-        <v>245.4949494949495</v>
+        <v>418.3303111889637</v>
       </c>
       <c r="W5" t="n">
-        <v>120.2424242424242</v>
+        <v>293.0777859364384</v>
       </c>
       <c r="X5" t="n">
-        <v>22.26580899333763</v>
+        <v>215.6330316951825</v>
       </c>
       <c r="Y5" t="n">
-        <v>22.26580899333763</v>
+        <v>103.1911805004286</v>
       </c>
     </row>
     <row r="6">
@@ -4637,10 +4637,10 @@
         <v>9.92</v>
       </c>
       <c r="J6" t="n">
-        <v>9.92</v>
+        <v>127.72</v>
       </c>
       <c r="K6" t="n">
-        <v>9.92</v>
+        <v>127.72</v>
       </c>
       <c r="L6" t="n">
         <v>127.72</v>
@@ -4658,19 +4658,19 @@
         <v>496</v>
       </c>
       <c r="Q6" t="n">
-        <v>375.5309881876231</v>
+        <v>496</v>
       </c>
       <c r="R6" t="n">
-        <v>253.2092184811984</v>
+        <v>373.6782302935753</v>
       </c>
       <c r="S6" t="n">
-        <v>193.8827081300568</v>
+        <v>313.3730366326729</v>
       </c>
       <c r="T6" t="n">
-        <v>190.187271565768</v>
+        <v>188.1205113801477</v>
       </c>
       <c r="U6" t="n">
-        <v>77.34075711791537</v>
+        <v>187.9360427830465</v>
       </c>
       <c r="V6" t="n">
         <v>62.68351753052128</v>
@@ -4692,49 +4692,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>255.44</v>
+        <v>142.0919516635869</v>
       </c>
       <c r="C7" t="n">
-        <v>255.44</v>
+        <v>264.8519516635869</v>
       </c>
       <c r="D7" t="n">
-        <v>255.44</v>
+        <v>378.171095788587</v>
       </c>
       <c r="E7" t="n">
-        <v>255.44</v>
+        <v>496</v>
       </c>
       <c r="F7" t="n">
-        <v>255.44</v>
+        <v>496</v>
       </c>
       <c r="G7" t="n">
-        <v>255.44</v>
+        <v>496</v>
       </c>
       <c r="H7" t="n">
-        <v>255.44</v>
+        <v>496</v>
       </c>
       <c r="I7" t="n">
-        <v>255.44</v>
+        <v>496</v>
       </c>
       <c r="J7" t="n">
-        <v>344.5303459745621</v>
+        <v>496</v>
       </c>
       <c r="K7" t="n">
-        <v>467.2903459745621</v>
+        <v>496</v>
       </c>
       <c r="L7" t="n">
         <v>496</v>
       </c>
       <c r="M7" t="n">
-        <v>430.113258891281</v>
+        <v>496</v>
       </c>
       <c r="N7" t="n">
-        <v>311.8317289761828</v>
+        <v>496</v>
       </c>
       <c r="O7" t="n">
-        <v>186.5792037236575</v>
+        <v>385.6775757575758</v>
       </c>
       <c r="P7" t="n">
-        <v>186.5792037236575</v>
+        <v>260.4250505050505</v>
       </c>
       <c r="Q7" t="n">
         <v>135.1725252525252</v>
@@ -4749,19 +4749,19 @@
         <v>9.92</v>
       </c>
       <c r="U7" t="n">
-        <v>9.92</v>
+        <v>30.33461399729475</v>
       </c>
       <c r="V7" t="n">
-        <v>132.68</v>
+        <v>30.33461399729475</v>
       </c>
       <c r="W7" t="n">
-        <v>255.44</v>
+        <v>30.33461399729475</v>
       </c>
       <c r="X7" t="n">
-        <v>255.44</v>
+        <v>30.33461399729475</v>
       </c>
       <c r="Y7" t="n">
-        <v>255.44</v>
+        <v>30.33461399729475</v>
       </c>
     </row>
     <row r="8">
@@ -4771,16 +4771,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>45.00346474573503</v>
+        <v>77.30602292005612</v>
       </c>
       <c r="C8" t="n">
-        <v>29.83034883506912</v>
+        <v>30.36200449278954</v>
       </c>
       <c r="D8" t="n">
-        <v>22.41706020895823</v>
+        <v>22.94871586667864</v>
       </c>
       <c r="E8" t="n">
-        <v>21.04</v>
+        <v>22.94871586667864</v>
       </c>
       <c r="F8" t="n">
         <v>21.04</v>
@@ -4804,13 +4804,13 @@
         <v>573.294066832436</v>
       </c>
       <c r="M8" t="n">
-        <v>617.8545487608372</v>
+        <v>573.294066832436</v>
       </c>
       <c r="N8" t="n">
-        <v>878.2245487608373</v>
+        <v>573.294066832436</v>
       </c>
       <c r="O8" t="n">
-        <v>940.1105430081138</v>
+        <v>833.664066832436</v>
       </c>
       <c r="P8" t="n">
         <v>1052</v>
@@ -4822,25 +4822,25 @@
         <v>1052</v>
       </c>
       <c r="S8" t="n">
-        <v>1052</v>
+        <v>1016.739618342616</v>
       </c>
       <c r="T8" t="n">
-        <v>869.9531558601888</v>
+        <v>834.6927742028047</v>
       </c>
       <c r="U8" t="n">
-        <v>621.3084474028844</v>
+        <v>586.0480657455004</v>
       </c>
       <c r="V8" t="n">
-        <v>392.1659987495269</v>
+        <v>586.0480657455004</v>
       </c>
       <c r="W8" t="n">
-        <v>154.4150129101859</v>
+        <v>348.2970799061594</v>
       </c>
       <c r="X8" t="n">
-        <v>154.4150129101859</v>
+        <v>157.1033087337677</v>
       </c>
       <c r="Y8" t="n">
-        <v>45.00346474573503</v>
+        <v>157.1033087337677</v>
       </c>
     </row>
     <row r="9">
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286.6965656565657</v>
+        <v>696.9483326296707</v>
       </c>
       <c r="C9" t="n">
-        <v>286.6965656565657</v>
+        <v>491.3544359108342</v>
       </c>
       <c r="D9" t="n">
-        <v>286.6965656565657</v>
+        <v>491.3544359108342</v>
       </c>
       <c r="E9" t="n">
-        <v>21.04</v>
+        <v>491.3544359108342</v>
       </c>
       <c r="F9" t="n">
-        <v>21.04</v>
+        <v>225.6978702542686</v>
       </c>
       <c r="G9" t="n">
-        <v>21.04</v>
+        <v>225.6978702542686</v>
       </c>
       <c r="H9" t="n">
-        <v>21.04</v>
+        <v>225.6978702542686</v>
       </c>
       <c r="I9" t="n">
         <v>21.04</v>
@@ -4877,16 +4877,16 @@
         <v>184.4287431941669</v>
       </c>
       <c r="K9" t="n">
-        <v>339.0314713795499</v>
+        <v>441.0175090998709</v>
       </c>
       <c r="L9" t="n">
-        <v>599.4014713795499</v>
+        <v>441.0175090998709</v>
       </c>
       <c r="M9" t="n">
-        <v>599.4014713795499</v>
+        <v>632.8498508427301</v>
       </c>
       <c r="N9" t="n">
-        <v>599.4014713795499</v>
+        <v>859.7714713795499</v>
       </c>
       <c r="O9" t="n">
         <v>859.7714713795499</v>
@@ -4898,28 +4898,28 @@
         <v>931.5309881876231</v>
       </c>
       <c r="R9" t="n">
-        <v>665.8744225310575</v>
+        <v>812.2395215115014</v>
       </c>
       <c r="S9" t="n">
-        <v>400.2178568744918</v>
+        <v>755.9433141906628</v>
       </c>
       <c r="T9" t="n">
-        <v>399.5527233405061</v>
+        <v>755.278180656677</v>
       </c>
       <c r="U9" t="n">
-        <v>399.5527233405061</v>
+        <v>755.278180656677</v>
       </c>
       <c r="V9" t="n">
-        <v>333.3994771264809</v>
+        <v>743.6512440995859</v>
       </c>
       <c r="W9" t="n">
-        <v>303.7296358034218</v>
+        <v>713.9814027765268</v>
       </c>
       <c r="X9" t="n">
-        <v>286.6965656565657</v>
+        <v>696.9483326296707</v>
       </c>
       <c r="Y9" t="n">
-        <v>286.6965656565657</v>
+        <v>696.9483326296707</v>
       </c>
     </row>
     <row r="10">
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1030.340019055067</v>
+        <v>424.5810695641195</v>
       </c>
       <c r="C10" t="n">
-        <v>1030.340019055067</v>
+        <v>452.9554063650766</v>
       </c>
       <c r="D10" t="n">
-        <v>1030.340019055067</v>
+        <v>569.2445504900767</v>
       </c>
       <c r="E10" t="n">
-        <v>1052</v>
+        <v>690.0434547014897</v>
       </c>
       <c r="F10" t="n">
-        <v>1052</v>
+        <v>817.3744272934252</v>
       </c>
       <c r="G10" t="n">
-        <v>1052</v>
+        <v>817.3744272934252</v>
       </c>
       <c r="H10" t="n">
-        <v>1052</v>
+        <v>817.3744272934252</v>
       </c>
       <c r="I10" t="n">
         <v>1052</v>
@@ -4965,16 +4965,16 @@
         <v>989.143561921584</v>
       </c>
       <c r="N10" t="n">
-        <v>873.8923350367888</v>
+        <v>985.8770449717642</v>
       </c>
       <c r="O10" t="n">
-        <v>684.5104604082094</v>
+        <v>796.4951703431848</v>
       </c>
       <c r="P10" t="n">
-        <v>440.368421378156</v>
+        <v>552.3531313131314</v>
       </c>
       <c r="Q10" t="n">
-        <v>174.7118557215903</v>
+        <v>286.6965656565657</v>
       </c>
       <c r="R10" t="n">
         <v>21.04</v>
@@ -4989,16 +4989,16 @@
         <v>270.580278539926</v>
       </c>
       <c r="V10" t="n">
-        <v>472.3716714258719</v>
+        <v>270.580278539926</v>
       </c>
       <c r="W10" t="n">
-        <v>647.2325896855493</v>
+        <v>270.580278539926</v>
       </c>
       <c r="X10" t="n">
-        <v>801.2333807097428</v>
+        <v>424.5810695641195</v>
       </c>
       <c r="Y10" t="n">
-        <v>915.6126813887751</v>
+        <v>424.5810695641195</v>
       </c>
     </row>
     <row r="11">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>129.2928845857069</v>
+        <v>25.92</v>
       </c>
       <c r="C11" t="n">
-        <v>129.2928845857069</v>
+        <v>25.92</v>
       </c>
       <c r="D11" t="n">
         <v>25.92</v>
@@ -5035,7 +5035,7 @@
         <v>346.68</v>
       </c>
       <c r="K11" t="n">
-        <v>667.4400000000001</v>
+        <v>480.7045487608373</v>
       </c>
       <c r="L11" t="n">
         <v>801.4645487608373</v>
@@ -5059,25 +5059,25 @@
         <v>1296</v>
       </c>
       <c r="S11" t="n">
-        <v>1125.401018259671</v>
+        <v>1296</v>
       </c>
       <c r="T11" t="n">
-        <v>847.3945781602636</v>
+        <v>1017.993559900593</v>
       </c>
       <c r="U11" t="n">
-        <v>847.3945781602636</v>
+        <v>690.7208326278519</v>
       </c>
       <c r="V11" t="n">
-        <v>522.2925335473101</v>
+        <v>365.6187880148985</v>
       </c>
       <c r="W11" t="n">
-        <v>416.4462517176945</v>
+        <v>365.6187880148985</v>
       </c>
       <c r="X11" t="n">
-        <v>129.2928845857069</v>
+        <v>78.46542088291091</v>
       </c>
       <c r="Y11" t="n">
-        <v>129.2928845857069</v>
+        <v>25.92</v>
       </c>
     </row>
     <row r="12">
@@ -5087,7 +5087,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>224.6678327447375</v>
+        <v>224.6678327447374</v>
       </c>
       <c r="C12" t="n">
         <v>171.0315575472432</v>
@@ -5096,13 +5096,13 @@
         <v>130.6904596707759</v>
       </c>
       <c r="E12" t="n">
-        <v>95.66813924460158</v>
+        <v>95.66813924460155</v>
       </c>
       <c r="F12" t="n">
-        <v>63.71233890331181</v>
+        <v>63.71233890331179</v>
       </c>
       <c r="G12" t="n">
-        <v>46.21945913627447</v>
+        <v>46.21945913627444</v>
       </c>
       <c r="H12" t="n">
         <v>25.92</v>
@@ -5111,13 +5111,13 @@
         <v>25.92</v>
       </c>
       <c r="J12" t="n">
-        <v>28.58810955742427</v>
+        <v>189.3087431941669</v>
       </c>
       <c r="K12" t="n">
-        <v>28.58810955742427</v>
+        <v>445.897509099871</v>
       </c>
       <c r="L12" t="n">
-        <v>349.3481095574243</v>
+        <v>541.1804513002835</v>
       </c>
       <c r="M12" t="n">
         <v>541.1804513002835</v>
@@ -5156,7 +5156,7 @@
         <v>394.3122260906576</v>
       </c>
       <c r="Y12" t="n">
-        <v>301.9976879430472</v>
+        <v>301.9976879430471</v>
       </c>
     </row>
     <row r="13">
@@ -5166,13 +5166,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>539.3296847471041</v>
+        <v>566.0785889585171</v>
       </c>
       <c r="C13" t="n">
-        <v>574.2516905655399</v>
+        <v>601.0005947769529</v>
       </c>
       <c r="D13" t="n">
-        <v>596.4908346905399</v>
+        <v>623.2397389019529</v>
       </c>
       <c r="E13" t="n">
         <v>623.2397389019529</v>
@@ -5196,25 +5196,25 @@
         <v>1296</v>
       </c>
       <c r="L13" t="n">
-        <v>1232.363283364389</v>
+        <v>1296</v>
       </c>
       <c r="M13" t="n">
-        <v>1073.547249326377</v>
+        <v>1177.017747978021</v>
       </c>
       <c r="N13" t="n">
-        <v>862.3364264819862</v>
+        <v>965.80692513363</v>
       </c>
       <c r="O13" t="n">
-        <v>576.9949558938108</v>
+        <v>680.4654545454546</v>
       </c>
       <c r="P13" t="n">
-        <v>401.8936754739888</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="Q13" t="n">
-        <v>401.8936754739888</v>
+        <v>25.92</v>
       </c>
       <c r="R13" t="n">
-        <v>74.62094820126148</v>
+        <v>25.92</v>
       </c>
       <c r="S13" t="n">
         <v>25.92</v>
@@ -5223,19 +5223,19 @@
         <v>124.4107414538868</v>
       </c>
       <c r="U13" t="n">
-        <v>249.8199442319628</v>
+        <v>279.9010199938128</v>
       </c>
       <c r="V13" t="n">
-        <v>357.5613371179088</v>
+        <v>387.6424128797588</v>
       </c>
       <c r="W13" t="n">
-        <v>438.3722553775862</v>
+        <v>468.4533311394362</v>
       </c>
       <c r="X13" t="n">
-        <v>498.3230464017797</v>
+        <v>528.4041221636297</v>
       </c>
       <c r="Y13" t="n">
-        <v>518.652347080812</v>
+        <v>545.401251292225</v>
       </c>
     </row>
     <row r="14">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>552.8261620330704</v>
+        <v>563.3301867537859</v>
       </c>
       <c r="C14" t="n">
-        <v>409.9225476462078</v>
+        <v>420.4265723669233</v>
       </c>
       <c r="D14" t="n">
-        <v>409.9225476462078</v>
+        <v>317.0536877812165</v>
       </c>
       <c r="E14" t="n">
-        <v>312.5858914776536</v>
+        <v>219.7170316126623</v>
       </c>
       <c r="F14" t="n">
-        <v>214.717579651379</v>
+        <v>121.8487197863876</v>
       </c>
       <c r="G14" t="n">
-        <v>118.7888598649914</v>
+        <v>25.92</v>
       </c>
       <c r="H14" t="n">
         <v>25.92</v>
@@ -5272,10 +5272,10 @@
         <v>57.43406683243596</v>
       </c>
       <c r="K14" t="n">
-        <v>378.1940668324359</v>
+        <v>159.9445487608373</v>
       </c>
       <c r="L14" t="n">
-        <v>698.9540668324358</v>
+        <v>480.7045487608373</v>
       </c>
       <c r="M14" t="n">
         <v>801.4645487608373</v>
@@ -5296,25 +5296,25 @@
         <v>1296</v>
       </c>
       <c r="S14" t="n">
-        <v>1296</v>
+        <v>1125.401018259671</v>
       </c>
       <c r="T14" t="n">
-        <v>1205.200933918751</v>
+        <v>888.4322313667394</v>
       </c>
       <c r="U14" t="n">
-        <v>1205.200933918751</v>
+        <v>888.4322313667394</v>
       </c>
       <c r="V14" t="n">
-        <v>880.0988893057977</v>
+        <v>563.3301867537859</v>
       </c>
       <c r="W14" t="n">
-        <v>552.8261620330704</v>
+        <v>563.3301867537859</v>
       </c>
       <c r="X14" t="n">
-        <v>552.8261620330704</v>
+        <v>563.3301867537859</v>
       </c>
       <c r="Y14" t="n">
-        <v>552.8261620330704</v>
+        <v>563.3301867537859</v>
       </c>
     </row>
     <row r="15">
@@ -5348,43 +5348,43 @@
         <v>25.92</v>
       </c>
       <c r="J15" t="n">
-        <v>25.92</v>
+        <v>189.3087431941669</v>
       </c>
       <c r="K15" t="n">
-        <v>282.5087659057041</v>
+        <v>445.897509099871</v>
       </c>
       <c r="L15" t="n">
-        <v>541.5766381778744</v>
+        <v>541.1804513002835</v>
       </c>
       <c r="M15" t="n">
-        <v>733.4089799207336</v>
+        <v>541.1804513002835</v>
       </c>
       <c r="N15" t="n">
-        <v>975.24</v>
+        <v>783.0114713795499</v>
       </c>
       <c r="O15" t="n">
-        <v>1296</v>
+        <v>1103.77147137955</v>
       </c>
       <c r="P15" t="n">
         <v>1296</v>
       </c>
       <c r="Q15" t="n">
-        <v>1296.000000000004</v>
+        <v>1296</v>
       </c>
       <c r="R15" t="n">
-        <v>1080.748937364287</v>
+        <v>1082.515156296862</v>
       </c>
       <c r="S15" t="n">
-        <v>928.4931340838521</v>
+        <v>930.2593530164277</v>
       </c>
       <c r="T15" t="n">
-        <v>831.8684045902703</v>
+        <v>833.6346235228459</v>
       </c>
       <c r="U15" t="n">
-        <v>738.7546430638762</v>
+        <v>740.5208619964518</v>
       </c>
       <c r="V15" t="n">
-        <v>631.1681105471891</v>
+        <v>632.9343294797648</v>
       </c>
       <c r="W15" t="n">
         <v>507.3048921971097</v>
@@ -5403,31 +5403,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>569.4107605089541</v>
+        <v>539.3296847471041</v>
       </c>
       <c r="C16" t="n">
-        <v>604.3327663273899</v>
+        <v>574.2516905655399</v>
       </c>
       <c r="D16" t="n">
-        <v>626.5719104523899</v>
+        <v>596.4908346905399</v>
       </c>
       <c r="E16" t="n">
-        <v>653.3208146638029</v>
+        <v>623.2397389019529</v>
       </c>
       <c r="F16" t="n">
-        <v>686.6017872557384</v>
+        <v>656.5207114938884</v>
       </c>
       <c r="G16" t="n">
-        <v>749.2782613393449</v>
+        <v>719.1971855774949</v>
       </c>
       <c r="H16" t="n">
-        <v>830.8258484659556</v>
+        <v>800.7447727041056</v>
       </c>
       <c r="I16" t="n">
-        <v>971.4014211725303</v>
+        <v>941.3203454106803</v>
       </c>
       <c r="J16" t="n">
-        <v>1266.143671333178</v>
+        <v>1236.062595571328</v>
       </c>
       <c r="K16" t="n">
         <v>1296</v>
@@ -5439,19 +5439,19 @@
         <v>1073.547249326377</v>
       </c>
       <c r="N16" t="n">
-        <v>862.3364264819862</v>
+        <v>1073.547249326377</v>
       </c>
       <c r="O16" t="n">
-        <v>862.3364264819862</v>
+        <v>788.205778738202</v>
       </c>
       <c r="P16" t="n">
-        <v>680.4654545454546</v>
+        <v>460.9330514654746</v>
       </c>
       <c r="Q16" t="n">
-        <v>353.1927272727273</v>
+        <v>133.6603241927473</v>
       </c>
       <c r="R16" t="n">
-        <v>25.92</v>
+        <v>74.6209482012615</v>
       </c>
       <c r="S16" t="n">
         <v>25.92</v>
@@ -5469,10 +5469,10 @@
         <v>468.4533311394362</v>
       </c>
       <c r="X16" t="n">
-        <v>528.4041221636297</v>
+        <v>498.3230464017797</v>
       </c>
       <c r="Y16" t="n">
-        <v>548.733422842662</v>
+        <v>518.652347080812</v>
       </c>
     </row>
     <row r="17">
@@ -5482,10 +5482,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.40739613105635</v>
+        <v>128.92631934605</v>
       </c>
       <c r="C17" t="n">
-        <v>58.40739613105635</v>
+        <v>73.90149283797533</v>
       </c>
       <c r="D17" t="n">
         <v>58.40739613105635</v>
@@ -5509,19 +5509,19 @@
         <v>57.43406683243596</v>
       </c>
       <c r="K17" t="n">
-        <v>357.6051827306865</v>
+        <v>378.1940668324359</v>
       </c>
       <c r="L17" t="n">
-        <v>480.7045487608373</v>
+        <v>698.9540668324358</v>
       </c>
       <c r="M17" t="n">
-        <v>801.4645487608373</v>
+        <v>698.9540668324358</v>
       </c>
       <c r="N17" t="n">
-        <v>1122.224548760837</v>
+        <v>698.9540668324358</v>
       </c>
       <c r="O17" t="n">
-        <v>1184.110543008114</v>
+        <v>975.24</v>
       </c>
       <c r="P17" t="n">
         <v>1296</v>
@@ -5542,16 +5542,16 @@
         <v>766.426637379727</v>
       </c>
       <c r="V17" t="n">
-        <v>529.2033806455614</v>
+        <v>533.5713487390284</v>
       </c>
       <c r="W17" t="n">
-        <v>283.3715867254124</v>
+        <v>533.5713487390284</v>
       </c>
       <c r="X17" t="n">
-        <v>84.09700747221265</v>
+        <v>334.2967694858287</v>
       </c>
       <c r="Y17" t="n">
-        <v>58.40739613105635</v>
+        <v>216.8044132405697</v>
       </c>
     </row>
     <row r="18">
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>557.8505975269959</v>
+        <v>1003.261772040771</v>
       </c>
       <c r="C18" t="n">
-        <v>557.8505975269959</v>
+        <v>680.4654545454546</v>
       </c>
       <c r="D18" t="n">
-        <v>557.8505975269959</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="E18" t="n">
-        <v>230.5778702542686</v>
+        <v>353.1927272727273</v>
       </c>
       <c r="F18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="G18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="H18" t="n">
-        <v>230.5778702542686</v>
+        <v>25.92</v>
       </c>
       <c r="I18" t="n">
         <v>25.92</v>
@@ -5588,19 +5588,19 @@
         <v>189.3087431941669</v>
       </c>
       <c r="K18" t="n">
-        <v>189.3087431941669</v>
+        <v>445.897509099871</v>
       </c>
       <c r="L18" t="n">
-        <v>349.3481095574243</v>
+        <v>766.657509099871</v>
       </c>
       <c r="M18" t="n">
-        <v>541.1804513002835</v>
+        <v>766.657509099871</v>
       </c>
       <c r="N18" t="n">
-        <v>783.0114713795499</v>
+        <v>1008.488529179137</v>
       </c>
       <c r="O18" t="n">
-        <v>1103.77147137955</v>
+        <v>1296</v>
       </c>
       <c r="P18" t="n">
         <v>1296</v>
@@ -5609,28 +5609,28 @@
         <v>1296</v>
       </c>
       <c r="R18" t="n">
-        <v>1045.254304354417</v>
+        <v>1168.62772524307</v>
       </c>
       <c r="S18" t="n">
-        <v>980.8772889527701</v>
+        <v>1104.250709841423</v>
       </c>
       <c r="T18" t="n">
-        <v>972.1313473379762</v>
+        <v>1095.50476822663</v>
       </c>
       <c r="U18" t="n">
-        <v>644.8586200652489</v>
+        <v>1090.269794579023</v>
       </c>
       <c r="V18" t="n">
-        <v>625.1508754273498</v>
+        <v>1070.562049941124</v>
       </c>
       <c r="W18" t="n">
-        <v>587.4002260234826</v>
+        <v>1032.811400537257</v>
       </c>
       <c r="X18" t="n">
-        <v>562.2863477958184</v>
+        <v>1007.697522309593</v>
       </c>
       <c r="Y18" t="n">
-        <v>557.8505975269959</v>
+        <v>1003.261772040771</v>
       </c>
     </row>
     <row r="19">
@@ -5640,31 +5640,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>132.3793006790323</v>
+        <v>1026.098219723011</v>
       </c>
       <c r="C19" t="n">
-        <v>204.0693106056562</v>
+        <v>1147.150225541447</v>
       </c>
       <c r="D19" t="n">
-        <v>312.4384547306562</v>
+        <v>1255.519369666447</v>
       </c>
       <c r="E19" t="n">
-        <v>312.4384547306562</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="F19" t="n">
-        <v>431.8494273225917</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="G19" t="n">
-        <v>431.8494273225917</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="H19" t="n">
-        <v>599.5270144492024</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="I19" t="n">
-        <v>826.2325871557771</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="J19" t="n">
-        <v>1146.992587155777</v>
+        <v>1293.059991584449</v>
       </c>
       <c r="K19" t="n">
         <v>1293.059991584449</v>
@@ -5691,25 +5691,25 @@
         <v>25.92</v>
       </c>
       <c r="S19" t="n">
-        <v>25.92</v>
+        <v>64.31820066794363</v>
       </c>
       <c r="T19" t="n">
-        <v>25.92</v>
+        <v>64.31820066794363</v>
       </c>
       <c r="U19" t="n">
-        <v>25.92</v>
+        <v>305.9384792078696</v>
       </c>
       <c r="V19" t="n">
-        <v>25.92</v>
+        <v>499.8098720938156</v>
       </c>
       <c r="W19" t="n">
-        <v>25.92</v>
+        <v>666.7507903534929</v>
       </c>
       <c r="X19" t="n">
-        <v>25.92</v>
+        <v>812.8315813776865</v>
       </c>
       <c r="Y19" t="n">
-        <v>132.3793006790323</v>
+        <v>919.2908820567187</v>
       </c>
     </row>
     <row r="20">
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86.25489849427822</v>
+        <v>124.2562473598465</v>
       </c>
       <c r="C20" t="n">
-        <v>31.23007198620355</v>
+        <v>69.23142085177179</v>
       </c>
       <c r="D20" t="n">
-        <v>31.23007198620355</v>
+        <v>53.73732414485281</v>
       </c>
       <c r="E20" t="n">
-        <v>31.23007198620355</v>
+        <v>44.2794558550865</v>
       </c>
       <c r="F20" t="n">
-        <v>31.23007198620355</v>
+        <v>34.28993190759977</v>
       </c>
       <c r="G20" t="n">
-        <v>31.23007198620355</v>
+        <v>26.24</v>
       </c>
       <c r="H20" t="n">
         <v>26.24</v>
@@ -5743,16 +5743,16 @@
         <v>26.24</v>
       </c>
       <c r="J20" t="n">
-        <v>350.9600000000005</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K20" t="n">
-        <v>675.6800000000005</v>
+        <v>382.4740668324359</v>
       </c>
       <c r="L20" t="n">
-        <v>1000.4</v>
+        <v>707.1940668324359</v>
       </c>
       <c r="M20" t="n">
-        <v>1138.224548760837</v>
+        <v>813.5045487608368</v>
       </c>
       <c r="N20" t="n">
         <v>1138.224548760837</v>
@@ -5770,25 +5770,25 @@
         <v>1312</v>
       </c>
       <c r="S20" t="n">
-        <v>1229.279806138459</v>
+        <v>1259.534916912672</v>
       </c>
       <c r="T20" t="n">
-        <v>1039.152153917839</v>
+        <v>1069.407264692052</v>
       </c>
       <c r="U20" t="n">
-        <v>782.4266373797268</v>
+        <v>812.6817481539398</v>
       </c>
       <c r="V20" t="n">
-        <v>545.2033806455612</v>
+        <v>575.4584914197742</v>
       </c>
       <c r="W20" t="n">
-        <v>299.3715867254122</v>
+        <v>329.6266974996252</v>
       </c>
       <c r="X20" t="n">
-        <v>100.0970074722124</v>
+        <v>329.6266974996252</v>
       </c>
       <c r="Y20" t="n">
-        <v>100.0970074722124</v>
+        <v>212.1343412543662</v>
       </c>
     </row>
     <row r="21">
@@ -5798,19 +5798,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.24</v>
+        <v>1019.261772040771</v>
       </c>
       <c r="C21" t="n">
-        <v>26.24</v>
+        <v>1019.261772040771</v>
       </c>
       <c r="D21" t="n">
-        <v>26.24</v>
+        <v>687.9486407276387</v>
       </c>
       <c r="E21" t="n">
-        <v>26.24</v>
+        <v>686.1571221912803</v>
       </c>
       <c r="F21" t="n">
-        <v>26.24</v>
+        <v>354.8439908781485</v>
       </c>
       <c r="G21" t="n">
         <v>26.24</v>
@@ -5828,46 +5828,46 @@
         <v>446.217509099871</v>
       </c>
       <c r="L21" t="n">
-        <v>446.217509099871</v>
+        <v>770.9375090998715</v>
       </c>
       <c r="M21" t="n">
-        <v>638.0498508427302</v>
+        <v>770.9375090998715</v>
       </c>
       <c r="N21" t="n">
-        <v>879.8808709219966</v>
+        <v>795.0514713795494</v>
       </c>
       <c r="O21" t="n">
-        <v>1204.600870921997</v>
+        <v>1119.77147137955</v>
       </c>
       <c r="P21" t="n">
         <v>1312</v>
       </c>
       <c r="Q21" t="n">
-        <v>1191.530988187623</v>
+        <v>1312</v>
       </c>
       <c r="R21" t="n">
-        <v>1064.158713430693</v>
+        <v>1184.62772524307</v>
       </c>
       <c r="S21" t="n">
-        <v>999.7816980290467</v>
+        <v>1120.250709841423</v>
       </c>
       <c r="T21" t="n">
-        <v>991.0357564142528</v>
+        <v>1111.50476822663</v>
       </c>
       <c r="U21" t="n">
-        <v>659.7226251011214</v>
+        <v>1106.269794579023</v>
       </c>
       <c r="V21" t="n">
-        <v>640.0148804632222</v>
+        <v>1086.562049941124</v>
       </c>
       <c r="W21" t="n">
-        <v>308.7017491500908</v>
+        <v>1048.811400537257</v>
       </c>
       <c r="X21" t="n">
-        <v>30.67575026882257</v>
+        <v>1023.697522309593</v>
       </c>
       <c r="Y21" t="n">
-        <v>26.24</v>
+        <v>1019.261772040771</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>385.587429369518</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="C22" t="n">
-        <v>506.6394351879537</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="D22" t="n">
-        <v>615.0085793129538</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="E22" t="n">
-        <v>727.8874835243668</v>
+        <v>159.9919806470492</v>
       </c>
       <c r="F22" t="n">
-        <v>847.2984561163023</v>
+        <v>279.4029532389847</v>
       </c>
       <c r="G22" t="n">
-        <v>996.1049301999088</v>
+        <v>428.2094273225912</v>
       </c>
       <c r="H22" t="n">
-        <v>1163.78251732652</v>
+        <v>595.8870144492018</v>
       </c>
       <c r="I22" t="n">
-        <v>1293.379991584449</v>
+        <v>822.5925871557765</v>
       </c>
       <c r="J22" t="n">
-        <v>1293.379991584449</v>
+        <v>1147.312587155777</v>
       </c>
       <c r="K22" t="n">
         <v>1293.379991584449</v>
@@ -5937,16 +5937,16 @@
         <v>26.24</v>
       </c>
       <c r="V22" t="n">
-        <v>26.24</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="W22" t="n">
-        <v>26.24</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="X22" t="n">
-        <v>172.3207910241935</v>
+        <v>47.11307643563613</v>
       </c>
       <c r="Y22" t="n">
-        <v>278.7800917032258</v>
+        <v>47.11307643563613</v>
       </c>
     </row>
     <row r="23">
@@ -5956,25 +5956,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>154.4841330900094</v>
+        <v>153.1081375278682</v>
       </c>
       <c r="C23" t="n">
-        <v>96.42900355163172</v>
+        <v>95.05300798949048</v>
       </c>
       <c r="D23" t="n">
-        <v>77.90460381440971</v>
+        <v>76.52860825226847</v>
       </c>
       <c r="E23" t="n">
-        <v>65.41643249434037</v>
+        <v>64.04043693219913</v>
       </c>
       <c r="F23" t="n">
-        <v>52.39660551655061</v>
+        <v>51.02060995440938</v>
       </c>
       <c r="G23" t="n">
-        <v>41.31637057864781</v>
+        <v>39.94037501650658</v>
       </c>
       <c r="H23" t="n">
-        <v>33.29599556214124</v>
+        <v>31.92</v>
       </c>
       <c r="I23" t="n">
         <v>31.92</v>
@@ -5983,19 +5983,19 @@
         <v>426.9300000000007</v>
       </c>
       <c r="K23" t="n">
-        <v>526.1565955778901</v>
+        <v>620.9946397225713</v>
       </c>
       <c r="L23" t="n">
-        <v>694.0905430081125</v>
+        <v>744.0940057527221</v>
       </c>
       <c r="M23" t="n">
-        <v>694.0905430081125</v>
+        <v>744.0940057527221</v>
       </c>
       <c r="N23" t="n">
-        <v>694.0905430081125</v>
+        <v>744.0940057527221</v>
       </c>
       <c r="O23" t="n">
-        <v>1089.100543008113</v>
+        <v>805.9799999999987</v>
       </c>
       <c r="P23" t="n">
         <v>1200.989999999999</v>
@@ -6004,28 +6004,28 @@
         <v>1596</v>
       </c>
       <c r="R23" t="n">
-        <v>1596</v>
+        <v>1594.624004437859</v>
       </c>
       <c r="S23" t="n">
-        <v>1510.249503108156</v>
+        <v>1508.873507546014</v>
       </c>
       <c r="T23" t="n">
-        <v>1317.091547857233</v>
+        <v>1315.715552295092</v>
       </c>
       <c r="U23" t="n">
-        <v>1057.335728288818</v>
+        <v>1055.959732726677</v>
       </c>
       <c r="V23" t="n">
-        <v>817.082168524349</v>
+        <v>815.7061729622078</v>
       </c>
       <c r="W23" t="n">
-        <v>568.2200715738969</v>
+        <v>566.8440760117558</v>
       </c>
       <c r="X23" t="n">
-        <v>365.9151892903942</v>
+        <v>364.5391937282529</v>
       </c>
       <c r="Y23" t="n">
-        <v>245.3925300148321</v>
+        <v>244.0165344526909</v>
       </c>
     </row>
     <row r="24">
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>31.92</v>
+        <v>1279.019347798346</v>
       </c>
       <c r="C24" t="n">
-        <v>31.92</v>
+        <v>914.2719614897405</v>
       </c>
       <c r="D24" t="n">
-        <v>31.92</v>
+        <v>562.8197525021621</v>
       </c>
       <c r="E24" t="n">
-        <v>31.92</v>
+        <v>216.6863209648766</v>
       </c>
       <c r="F24" t="n">
         <v>31.92</v>
@@ -6059,19 +6059,19 @@
         <v>31.92</v>
       </c>
       <c r="J24" t="n">
-        <v>31.92</v>
+        <v>195.3087431941669</v>
       </c>
       <c r="K24" t="n">
-        <v>288.5087659057041</v>
+        <v>451.897509099871</v>
       </c>
       <c r="L24" t="n">
-        <v>650.4813991990175</v>
+        <v>813.8701423931843</v>
       </c>
       <c r="M24" t="n">
-        <v>842.3137409418766</v>
+        <v>1005.702484136043</v>
       </c>
       <c r="N24" t="n">
-        <v>1084.144761021143</v>
+        <v>1065.426303846774</v>
       </c>
       <c r="O24" t="n">
         <v>1403.77147137955</v>
@@ -6098,13 +6098,13 @@
         <v>1355.410534789609</v>
       </c>
       <c r="W24" t="n">
-        <v>1226.421572370028</v>
+        <v>1314.629582355439</v>
       </c>
       <c r="X24" t="n">
-        <v>823.3912693397247</v>
+        <v>1286.485401097472</v>
       </c>
       <c r="Y24" t="n">
-        <v>420.3609663094209</v>
+        <v>1279.019347798346</v>
       </c>
     </row>
     <row r="25">
@@ -6114,28 +6114,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>983.8517556114178</v>
+        <v>565.3313028377605</v>
       </c>
       <c r="C25" t="n">
-        <v>1101.933761429854</v>
+        <v>565.3313028377605</v>
       </c>
       <c r="D25" t="n">
-        <v>1207.332905554854</v>
+        <v>565.3313028377605</v>
       </c>
       <c r="E25" t="n">
-        <v>1317.241809766267</v>
+        <v>599.1630143071085</v>
       </c>
       <c r="F25" t="n">
-        <v>1317.241809766267</v>
+        <v>715.603986899044</v>
       </c>
       <c r="G25" t="n">
-        <v>1317.241809766267</v>
+        <v>715.603986899044</v>
       </c>
       <c r="H25" t="n">
-        <v>1317.241809766267</v>
+        <v>715.603986899044</v>
       </c>
       <c r="I25" t="n">
-        <v>1317.241809766267</v>
+        <v>939.3395596056187</v>
       </c>
       <c r="J25" t="n">
         <v>1317.241809766267</v>
@@ -6165,25 +6165,25 @@
         <v>31.92</v>
       </c>
       <c r="S25" t="n">
-        <v>31.92</v>
+        <v>67.34820066794363</v>
       </c>
       <c r="T25" t="n">
-        <v>39.89173655635062</v>
+        <v>67.34820066794363</v>
       </c>
       <c r="U25" t="n">
-        <v>278.5420150962766</v>
+        <v>67.34820066794363</v>
       </c>
       <c r="V25" t="n">
-        <v>469.4434079822225</v>
+        <v>258.2495935538896</v>
       </c>
       <c r="W25" t="n">
-        <v>633.4143262419</v>
+        <v>422.220511813567</v>
       </c>
       <c r="X25" t="n">
-        <v>776.5251172660935</v>
+        <v>565.3313028377605</v>
       </c>
       <c r="Y25" t="n">
-        <v>880.0144179451257</v>
+        <v>565.3313028377605</v>
       </c>
     </row>
     <row r="26">
@@ -6193,13 +6193,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>470.3539346256357</v>
+        <v>464.3177062084831</v>
       </c>
       <c r="C26" t="n">
-        <v>326.4402192286722</v>
+        <v>320.4039908115195</v>
       </c>
       <c r="D26" t="n">
-        <v>222.0572336328643</v>
+        <v>320.4039908115195</v>
       </c>
       <c r="E26" t="n">
         <v>222.0572336328643</v>
@@ -6217,25 +6217,25 @@
         <v>26.24</v>
       </c>
       <c r="J26" t="n">
-        <v>350.96</v>
+        <v>57.75406683243596</v>
       </c>
       <c r="K26" t="n">
-        <v>675.6800000000001</v>
+        <v>382.4740668324359</v>
       </c>
       <c r="L26" t="n">
-        <v>813.5045487608372</v>
+        <v>707.1940668324359</v>
       </c>
       <c r="M26" t="n">
-        <v>813.5045487608372</v>
+        <v>707.1940668324359</v>
       </c>
       <c r="N26" t="n">
-        <v>1138.224548760837</v>
+        <v>707.1940668324359</v>
       </c>
       <c r="O26" t="n">
-        <v>1200.110543008114</v>
+        <v>769.0800610797124</v>
       </c>
       <c r="P26" t="n">
-        <v>1312</v>
+        <v>1093.800061079713</v>
       </c>
       <c r="Q26" t="n">
         <v>1312</v>
@@ -6244,25 +6244,25 @@
         <v>1312</v>
       </c>
       <c r="S26" t="n">
-        <v>1312</v>
+        <v>1140.39091724957</v>
       </c>
       <c r="T26" t="n">
-        <v>1312</v>
+        <v>1140.39091724957</v>
       </c>
       <c r="U26" t="n">
-        <v>1084.629548390779</v>
+        <v>1140.39091724957</v>
       </c>
       <c r="V26" t="n">
-        <v>758.5174027677243</v>
+        <v>814.2787716265154</v>
       </c>
       <c r="W26" t="n">
-        <v>758.5174027677243</v>
+        <v>814.2787716265154</v>
       </c>
       <c r="X26" t="n">
-        <v>470.3539346256357</v>
+        <v>670.6989513426309</v>
       </c>
       <c r="Y26" t="n">
-        <v>470.3539346256357</v>
+        <v>464.3177062084831</v>
       </c>
     </row>
     <row r="27">
@@ -6302,16 +6302,16 @@
         <v>446.217509099871</v>
       </c>
       <c r="L27" t="n">
-        <v>446.217509099871</v>
+        <v>770.937509099871</v>
       </c>
       <c r="M27" t="n">
-        <v>638.0498508427302</v>
+        <v>962.7698508427302</v>
       </c>
       <c r="N27" t="n">
-        <v>879.8808709219966</v>
+        <v>987.28</v>
       </c>
       <c r="O27" t="n">
-        <v>1119.77147137955</v>
+        <v>1312</v>
       </c>
       <c r="P27" t="n">
         <v>1312</v>
@@ -6384,19 +6384,19 @@
         <v>1245.914258116138</v>
       </c>
       <c r="M28" t="n">
-        <v>1086.088123068025</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="N28" t="n">
-        <v>873.8671992135332</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="O28" t="n">
-        <v>587.5156276152568</v>
+        <v>1069.890443150791</v>
       </c>
       <c r="P28" t="n">
-        <v>587.5156276152568</v>
+        <v>738.5773118376464</v>
       </c>
       <c r="Q28" t="n">
-        <v>256.2024963021126</v>
+        <v>407.2641805245026</v>
       </c>
       <c r="R28" t="n">
         <v>75.95104921136252</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>130.6229855958079</v>
+        <v>448.1934779296424</v>
       </c>
       <c r="C29" t="n">
-        <v>130.6229855958079</v>
+        <v>421.7271164859311</v>
       </c>
       <c r="D29" t="n">
-        <v>26.24</v>
+        <v>317.3441308901232</v>
       </c>
       <c r="E29" t="n">
-        <v>26.24</v>
+        <v>218.997373711468</v>
       </c>
       <c r="F29" t="n">
-        <v>26.24</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="G29" t="n">
-        <v>26.24</v>
+        <v>120.1189608750924</v>
       </c>
       <c r="H29" t="n">
         <v>26.24</v>
@@ -6454,25 +6454,25 @@
         <v>26.24</v>
       </c>
       <c r="J29" t="n">
-        <v>57.75406683243596</v>
+        <v>350.9600000000009</v>
       </c>
       <c r="K29" t="n">
-        <v>382.4740668324359</v>
+        <v>675.680000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>707.1940668324359</v>
+        <v>798.7793660301517</v>
       </c>
       <c r="M29" t="n">
-        <v>813.5045487608363</v>
+        <v>798.7793660301518</v>
       </c>
       <c r="N29" t="n">
-        <v>1138.224548760837</v>
+        <v>798.7793660301518</v>
       </c>
       <c r="O29" t="n">
-        <v>1200.110543008114</v>
+        <v>860.6653602774284</v>
       </c>
       <c r="P29" t="n">
-        <v>1312</v>
+        <v>987.2799999999991</v>
       </c>
       <c r="Q29" t="n">
         <v>1312</v>
@@ -6487,19 +6487,19 @@
         <v>1312</v>
       </c>
       <c r="U29" t="n">
-        <v>1282.592975808249</v>
+        <v>980.6868686868447</v>
       </c>
       <c r="V29" t="n">
-        <v>956.4808301851946</v>
+        <v>654.5747230637903</v>
       </c>
       <c r="W29" t="n">
-        <v>625.1676988720444</v>
+        <v>654.5747230637903</v>
       </c>
       <c r="X29" t="n">
-        <v>337.0042307299558</v>
+        <v>654.5747230637903</v>
       </c>
       <c r="Y29" t="n">
-        <v>130.6229855958079</v>
+        <v>448.1934779296424</v>
       </c>
     </row>
     <row r="30">
@@ -6533,19 +6533,19 @@
         <v>26.24</v>
       </c>
       <c r="J30" t="n">
-        <v>189.6287431941669</v>
+        <v>26.24</v>
       </c>
       <c r="K30" t="n">
-        <v>189.6287431941669</v>
+        <v>282.8287659057041</v>
       </c>
       <c r="L30" t="n">
-        <v>514.3487431941678</v>
+        <v>607.5487659057051</v>
       </c>
       <c r="M30" t="n">
-        <v>706.181084937027</v>
+        <v>607.5487659057051</v>
       </c>
       <c r="N30" t="n">
-        <v>948.0121050162934</v>
+        <v>849.3797859849715</v>
       </c>
       <c r="O30" t="n">
         <v>1119.77147137955</v>
@@ -6554,22 +6554,22 @@
         <v>1312</v>
       </c>
       <c r="Q30" t="n">
-        <v>1312</v>
+        <v>1312.000000000011</v>
       </c>
       <c r="R30" t="n">
-        <v>1095.738836354181</v>
+        <v>1096.976570438276</v>
       </c>
       <c r="S30" t="n">
-        <v>942.4729320636458</v>
+        <v>943.7106661477408</v>
       </c>
       <c r="T30" t="n">
-        <v>844.8381015599631</v>
+        <v>846.0758356440581</v>
       </c>
       <c r="U30" t="n">
-        <v>750.7142390234679</v>
+        <v>751.9519731075629</v>
       </c>
       <c r="V30" t="n">
-        <v>642.1176054966799</v>
+        <v>643.3553395807749</v>
       </c>
       <c r="W30" t="n">
         <v>516.7158012880187</v>
@@ -6618,22 +6618,22 @@
         <v>1310.56107576185</v>
       </c>
       <c r="L31" t="n">
-        <v>1310.56107576185</v>
+        <v>1245.914258116138</v>
       </c>
       <c r="M31" t="n">
-        <v>1150.734940713737</v>
+        <v>1086.088123068025</v>
       </c>
       <c r="N31" t="n">
-        <v>938.514016859245</v>
+        <v>873.8671992135332</v>
       </c>
       <c r="O31" t="n">
-        <v>652.1624452609685</v>
+        <v>873.8671992135332</v>
       </c>
       <c r="P31" t="n">
-        <v>320.8493139478104</v>
+        <v>542.5540679003745</v>
       </c>
       <c r="Q31" t="n">
-        <v>26.24</v>
+        <v>211.2409365872138</v>
       </c>
       <c r="R31" t="n">
         <v>26.24</v>
@@ -6694,7 +6694,7 @@
         <v>46.71406683243596</v>
       </c>
       <c r="K32" t="n">
-        <v>234.8140668324359</v>
+        <v>210.0245487608342</v>
       </c>
       <c r="L32" t="n">
         <v>398.1245487608342</v>
@@ -6721,13 +6721,13 @@
         <v>747.9868768455293</v>
       </c>
       <c r="T32" t="n">
-        <v>735.3831723429812</v>
+        <v>628.5662953319807</v>
       </c>
       <c r="U32" t="n">
-        <v>549.3647265119395</v>
+        <v>442.5478495009389</v>
       </c>
       <c r="V32" t="n">
-        <v>382.8485404848446</v>
+        <v>276.0316634738441</v>
       </c>
       <c r="W32" t="n">
         <v>207.7238172717663</v>
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>703.3347959501409</v>
+        <v>399.03838383839</v>
       </c>
       <c r="C33" t="n">
-        <v>703.3347959501409</v>
+        <v>399.03838383839</v>
       </c>
       <c r="D33" t="n">
-        <v>703.3347959501409</v>
+        <v>207.119191919195</v>
       </c>
       <c r="E33" t="n">
-        <v>703.3347959501409</v>
+        <v>15.2</v>
       </c>
       <c r="F33" t="n">
-        <v>590.957575757585</v>
+        <v>15.2</v>
       </c>
       <c r="G33" t="n">
-        <v>399.03838383839</v>
+        <v>15.2</v>
       </c>
       <c r="H33" t="n">
-        <v>207.119191919195</v>
+        <v>15.2</v>
       </c>
       <c r="I33" t="n">
         <v>15.2</v>
       </c>
       <c r="J33" t="n">
-        <v>15.2</v>
+        <v>178.5887431941669</v>
       </c>
       <c r="K33" t="n">
-        <v>203.300000000003</v>
+        <v>366.6887431941699</v>
       </c>
       <c r="L33" t="n">
-        <v>203.300000000003</v>
+        <v>554.7887431941729</v>
       </c>
       <c r="M33" t="n">
-        <v>391.400000000006</v>
+        <v>554.7887431941729</v>
       </c>
       <c r="N33" t="n">
-        <v>571.899999999997</v>
+        <v>742.8887431941758</v>
       </c>
       <c r="O33" t="n">
-        <v>571.899999999997</v>
+        <v>742.8887431941758</v>
       </c>
       <c r="P33" t="n">
         <v>760</v>
       </c>
       <c r="Q33" t="n">
-        <v>760</v>
+        <v>639.5309881876231</v>
       </c>
       <c r="R33" t="n">
-        <v>703.3347959501409</v>
+        <v>582.865784137764</v>
       </c>
       <c r="S33" t="n">
-        <v>703.3347959501409</v>
+        <v>582.865784137764</v>
       </c>
       <c r="T33" t="n">
-        <v>703.3347959501409</v>
+        <v>582.865784137764</v>
       </c>
       <c r="U33" t="n">
-        <v>703.3347959501409</v>
+        <v>582.865784137764</v>
       </c>
       <c r="V33" t="n">
-        <v>703.3347959501409</v>
+        <v>582.865784137764</v>
       </c>
       <c r="W33" t="n">
-        <v>703.3347959501409</v>
+        <v>399.03838383839</v>
       </c>
       <c r="X33" t="n">
-        <v>703.3347959501409</v>
+        <v>399.03838383839</v>
       </c>
       <c r="Y33" t="n">
-        <v>703.3347959501409</v>
+        <v>399.03838383839</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>478.840345974559</v>
+        <v>755.6073376663011</v>
       </c>
       <c r="C34" t="n">
-        <v>478.840345974559</v>
+        <v>755.6073376663011</v>
       </c>
       <c r="D34" t="n">
-        <v>478.840345974559</v>
+        <v>760</v>
       </c>
       <c r="E34" t="n">
-        <v>478.840345974559</v>
+        <v>760</v>
       </c>
       <c r="F34" t="n">
-        <v>478.840345974559</v>
+        <v>760</v>
       </c>
       <c r="G34" t="n">
-        <v>478.840345974559</v>
+        <v>760</v>
       </c>
       <c r="H34" t="n">
-        <v>666.940345974562</v>
+        <v>760</v>
       </c>
       <c r="I34" t="n">
-        <v>666.940345974562</v>
+        <v>760</v>
       </c>
       <c r="J34" t="n">
-        <v>666.940345974562</v>
+        <v>760</v>
       </c>
       <c r="K34" t="n">
-        <v>666.940345974562</v>
+        <v>760</v>
       </c>
       <c r="L34" t="n">
         <v>760</v>
       </c>
       <c r="M34" t="n">
-        <v>759.7698245478466</v>
+        <v>759.9347365031441</v>
       </c>
       <c r="N34" t="n">
-        <v>707.1448602893141</v>
+        <v>707.3097722446116</v>
       </c>
       <c r="O34" t="n">
-        <v>580.3892482869973</v>
+        <v>580.5541602422948</v>
       </c>
       <c r="P34" t="n">
-        <v>398.8734718832065</v>
+        <v>399.038383838504</v>
       </c>
       <c r="Q34" t="n">
-        <v>207.119191919248</v>
+        <v>207.1191919192516</v>
       </c>
       <c r="R34" t="n">
         <v>15.2</v>
       </c>
       <c r="S34" t="n">
-        <v>122.8982006679436</v>
+        <v>15.2</v>
       </c>
       <c r="T34" t="n">
-        <v>290.740345974556</v>
+        <v>203.300000000003</v>
       </c>
       <c r="U34" t="n">
-        <v>478.840345974559</v>
+        <v>203.300000000003</v>
       </c>
       <c r="V34" t="n">
-        <v>478.840345974559</v>
+        <v>391.400000000006</v>
       </c>
       <c r="W34" t="n">
-        <v>478.840345974559</v>
+        <v>579.500000000009</v>
       </c>
       <c r="X34" t="n">
-        <v>478.840345974559</v>
+        <v>579.500000000009</v>
       </c>
       <c r="Y34" t="n">
-        <v>478.840345974559</v>
+        <v>579.500000000009</v>
       </c>
     </row>
     <row r="35">
@@ -6931,13 +6931,13 @@
         <v>41.83406683243596</v>
       </c>
       <c r="K35" t="n">
-        <v>169.544066832436</v>
+        <v>141.0606624103254</v>
       </c>
       <c r="L35" t="n">
-        <v>292.6434328625867</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="M35" t="n">
-        <v>342.2245487608371</v>
+        <v>264.1600284404761</v>
       </c>
       <c r="N35" t="n">
         <v>342.2245487608371</v>
@@ -6955,25 +6955,25 @@
         <v>516</v>
       </c>
       <c r="S35" t="n">
-        <v>503.9868768455294</v>
+        <v>516</v>
       </c>
       <c r="T35" t="n">
-        <v>503.9868768455294</v>
+        <v>448.0143764475027</v>
       </c>
       <c r="U35" t="n">
-        <v>373.6838465424257</v>
+        <v>317.7113461443917</v>
       </c>
       <c r="V35" t="n">
-        <v>333.1468475748582</v>
+        <v>187.4083158412875</v>
       </c>
       <c r="W35" t="n">
-        <v>202.8438172717663</v>
+        <v>57.10528553818827</v>
       </c>
       <c r="X35" t="n">
-        <v>74.27630872563728</v>
+        <v>57.10528553818827</v>
       </c>
       <c r="Y35" t="n">
-        <v>27.491023187449</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="36">
@@ -6983,16 +6983,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>270.9260606060717</v>
+        <v>255.3939393939283</v>
       </c>
       <c r="C36" t="n">
+        <v>255.3939393939283</v>
+      </c>
+      <c r="D36" t="n">
+        <v>255.3939393939283</v>
+      </c>
+      <c r="E36" t="n">
         <v>140.6230303030358</v>
-      </c>
-      <c r="D36" t="n">
-        <v>140.6230303030358</v>
-      </c>
-      <c r="E36" t="n">
-        <v>10.32</v>
       </c>
       <c r="F36" t="n">
         <v>10.32</v>
@@ -7013,16 +7013,16 @@
         <v>265.7400000000109</v>
       </c>
       <c r="L36" t="n">
+        <v>265.7400000000109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>265.7400000000109</v>
+      </c>
+      <c r="N36" t="n">
         <v>393.4500000000163</v>
       </c>
-      <c r="M36" t="n">
-        <v>516</v>
-      </c>
-      <c r="N36" t="n">
-        <v>516</v>
-      </c>
       <c r="O36" t="n">
-        <v>516</v>
+        <v>393.4500000000163</v>
       </c>
       <c r="P36" t="n">
         <v>516</v>
@@ -7031,28 +7031,28 @@
         <v>516</v>
       </c>
       <c r="R36" t="n">
-        <v>459.334795950141</v>
+        <v>385.6969696969642</v>
       </c>
       <c r="S36" t="n">
-        <v>329.0317656471051</v>
+        <v>385.6969696969642</v>
       </c>
       <c r="T36" t="n">
-        <v>329.0317656471051</v>
+        <v>385.6969696969642</v>
       </c>
       <c r="U36" t="n">
-        <v>329.0317656471051</v>
+        <v>255.3939393939283</v>
       </c>
       <c r="V36" t="n">
-        <v>270.9260606060717</v>
+        <v>255.3939393939283</v>
       </c>
       <c r="W36" t="n">
-        <v>270.9260606060717</v>
+        <v>255.3939393939283</v>
       </c>
       <c r="X36" t="n">
-        <v>270.9260606060717</v>
+        <v>255.3939393939283</v>
       </c>
       <c r="Y36" t="n">
-        <v>270.9260606060717</v>
+        <v>255.3939393939283</v>
       </c>
     </row>
     <row r="37">
@@ -7071,22 +7071,22 @@
         <v>260.5799999999891</v>
       </c>
       <c r="E37" t="n">
-        <v>260.5799999999891</v>
+        <v>388.2899999999946</v>
       </c>
       <c r="F37" t="n">
-        <v>388.2899999999946</v>
+        <v>516</v>
       </c>
       <c r="G37" t="n">
-        <v>388.2899999999946</v>
+        <v>516</v>
       </c>
       <c r="H37" t="n">
-        <v>388.2899999999946</v>
+        <v>516</v>
       </c>
       <c r="I37" t="n">
-        <v>388.2899999999946</v>
+        <v>516</v>
       </c>
       <c r="J37" t="n">
-        <v>388.2899999999946</v>
+        <v>516</v>
       </c>
       <c r="K37" t="n">
         <v>516</v>
@@ -7104,34 +7104,34 @@
         <v>336.6194237391506</v>
       </c>
       <c r="P37" t="n">
-        <v>206.3163934360424</v>
+        <v>206.3163934360313</v>
       </c>
       <c r="Q37" t="n">
-        <v>76.01336313293811</v>
+        <v>140.6230303031128</v>
       </c>
       <c r="R37" t="n">
         <v>10.32</v>
       </c>
       <c r="S37" t="n">
-        <v>118.0182006679436</v>
+        <v>10.32</v>
       </c>
       <c r="T37" t="n">
-        <v>118.0182006679436</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="U37" t="n">
-        <v>245.7282006679491</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="V37" t="n">
-        <v>245.7282006679491</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="W37" t="n">
-        <v>245.7282006679491</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="X37" t="n">
-        <v>245.7282006679491</v>
+        <v>138.0300000000054</v>
       </c>
       <c r="Y37" t="n">
-        <v>245.7282006679491</v>
+        <v>260.5799999999891</v>
       </c>
     </row>
     <row r="38">
@@ -7192,25 +7192,25 @@
         <v>516</v>
       </c>
       <c r="S38" t="n">
-        <v>503.9868768455294</v>
+        <v>516</v>
       </c>
       <c r="T38" t="n">
-        <v>384.5662953319808</v>
+        <v>516</v>
       </c>
       <c r="U38" t="n">
-        <v>333.1468475748709</v>
+        <v>385.6969696968591</v>
       </c>
       <c r="V38" t="n">
-        <v>202.8438172717663</v>
+        <v>269.1905388492537</v>
       </c>
       <c r="W38" t="n">
-        <v>202.8438172717663</v>
+        <v>138.887508546129</v>
       </c>
       <c r="X38" t="n">
-        <v>74.27630872563728</v>
+        <v>10.32</v>
       </c>
       <c r="Y38" t="n">
-        <v>27.491023187449</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="39">
@@ -7223,7 +7223,7 @@
         <v>140.6230303030395</v>
       </c>
       <c r="C39" t="n">
-        <v>140.6230303030395</v>
+        <v>10.32</v>
       </c>
       <c r="D39" t="n">
         <v>10.32</v>
@@ -7244,22 +7244,22 @@
         <v>10.32</v>
       </c>
       <c r="J39" t="n">
-        <v>10.32</v>
+        <v>138.030000000009</v>
       </c>
       <c r="K39" t="n">
-        <v>10.32</v>
+        <v>265.7400000000181</v>
       </c>
       <c r="L39" t="n">
-        <v>138.030000000009</v>
+        <v>388.289999999991</v>
       </c>
       <c r="M39" t="n">
-        <v>265.7400000000181</v>
+        <v>388.289999999991</v>
       </c>
       <c r="N39" t="n">
         <v>388.289999999991</v>
       </c>
       <c r="O39" t="n">
-        <v>388.289999999991</v>
+        <v>516</v>
       </c>
       <c r="P39" t="n">
         <v>516</v>
@@ -7286,7 +7286,7 @@
         <v>401.2290909091186</v>
       </c>
       <c r="X39" t="n">
-        <v>270.926060606079</v>
+        <v>401.2290909091186</v>
       </c>
       <c r="Y39" t="n">
         <v>270.926060606079</v>
@@ -7299,22 +7299,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>167.520345974544</v>
+        <v>245.7282006679526</v>
       </c>
       <c r="C40" t="n">
-        <v>167.520345974544</v>
+        <v>373.4382006679617</v>
       </c>
       <c r="D40" t="n">
-        <v>167.520345974544</v>
+        <v>373.4382006679617</v>
       </c>
       <c r="E40" t="n">
-        <v>167.520345974544</v>
+        <v>373.4382006679617</v>
       </c>
       <c r="F40" t="n">
-        <v>295.230345974553</v>
+        <v>422.940345974562</v>
       </c>
       <c r="G40" t="n">
-        <v>295.230345974553</v>
+        <v>422.940345974562</v>
       </c>
       <c r="H40" t="n">
         <v>422.940345974562</v>
@@ -7332,43 +7332,43 @@
         <v>516</v>
       </c>
       <c r="M40" t="n">
-        <v>516</v>
+        <v>515.7698245478466</v>
       </c>
       <c r="N40" t="n">
-        <v>463.3750357414675</v>
+        <v>463.1448602893141</v>
       </c>
       <c r="O40" t="n">
-        <v>336.6194237391507</v>
+        <v>336.3892482869973</v>
       </c>
       <c r="P40" t="n">
-        <v>206.3163934360091</v>
+        <v>206.0862179838483</v>
       </c>
       <c r="Q40" t="n">
-        <v>76.01336313287129</v>
+        <v>140.6230303031351</v>
       </c>
       <c r="R40" t="n">
         <v>10.32</v>
       </c>
       <c r="S40" t="n">
-        <v>10.32</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="T40" t="n">
-        <v>10.32</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="U40" t="n">
-        <v>10.32</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="V40" t="n">
-        <v>10.32</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="W40" t="n">
-        <v>10.32</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="X40" t="n">
-        <v>39.81034597453497</v>
+        <v>118.0182006679436</v>
       </c>
       <c r="Y40" t="n">
-        <v>167.520345974544</v>
+        <v>245.7282006679526</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>385.6969696968002</v>
+        <v>140.6230303030469</v>
       </c>
       <c r="C41" t="n">
-        <v>385.6969696968002</v>
+        <v>140.6230303030469</v>
       </c>
       <c r="D41" t="n">
-        <v>270.9260606062502</v>
+        <v>10.32</v>
       </c>
       <c r="E41" t="n">
-        <v>270.9260606062502</v>
+        <v>10.32</v>
       </c>
       <c r="F41" t="n">
-        <v>140.6230303032033</v>
+        <v>10.32</v>
       </c>
       <c r="G41" t="n">
-        <v>140.6230303032033</v>
+        <v>10.32</v>
       </c>
       <c r="H41" t="n">
         <v>10.32</v>
@@ -7408,7 +7408,7 @@
         <v>169.544066832436</v>
       </c>
       <c r="L41" t="n">
-        <v>292.6434328625867</v>
+        <v>297.254066832436</v>
       </c>
       <c r="M41" t="n">
         <v>342.2245487608371</v>
@@ -7429,25 +7429,25 @@
         <v>516</v>
       </c>
       <c r="S41" t="n">
-        <v>385.6969696968002</v>
+        <v>385.6969696967857</v>
       </c>
       <c r="T41" t="n">
-        <v>385.6969696968002</v>
+        <v>385.6969696967857</v>
       </c>
       <c r="U41" t="n">
-        <v>385.6969696968002</v>
+        <v>385.6969696967857</v>
       </c>
       <c r="V41" t="n">
-        <v>385.6969696968002</v>
+        <v>385.6969696967857</v>
       </c>
       <c r="W41" t="n">
-        <v>385.6969696968002</v>
+        <v>385.6969696967857</v>
       </c>
       <c r="X41" t="n">
-        <v>385.6969696968002</v>
+        <v>270.9260606060938</v>
       </c>
       <c r="Y41" t="n">
-        <v>385.6969696968002</v>
+        <v>270.9260606060938</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>10.32</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="C42" t="n">
-        <v>10.32</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="D42" t="n">
-        <v>10.32</v>
+        <v>189.8479867502915</v>
       </c>
       <c r="E42" t="n">
-        <v>10.32</v>
+        <v>189.8479867502915</v>
       </c>
       <c r="F42" t="n">
-        <v>10.32</v>
+        <v>94.25582277263808</v>
       </c>
       <c r="G42" t="n">
-        <v>10.32</v>
+        <v>94.25582277263808</v>
       </c>
       <c r="H42" t="n">
         <v>10.32</v>
@@ -7487,16 +7487,16 @@
         <v>138.0300000000162</v>
       </c>
       <c r="L42" t="n">
-        <v>265.7400000000325</v>
+        <v>260.5799999999675</v>
       </c>
       <c r="M42" t="n">
-        <v>393.4500000000487</v>
+        <v>260.5799999999675</v>
       </c>
       <c r="N42" t="n">
-        <v>393.4500000000487</v>
+        <v>260.5799999999675</v>
       </c>
       <c r="O42" t="n">
-        <v>516</v>
+        <v>388.2899999999838</v>
       </c>
       <c r="P42" t="n">
         <v>516</v>
@@ -7505,28 +7505,28 @@
         <v>516</v>
       </c>
       <c r="R42" t="n">
-        <v>385.6969696967938</v>
+        <v>516</v>
       </c>
       <c r="S42" t="n">
-        <v>270.9260606063469</v>
+        <v>516</v>
       </c>
       <c r="T42" t="n">
-        <v>270.9260606063469</v>
+        <v>424.1284785663352</v>
       </c>
       <c r="U42" t="n">
-        <v>270.9260606063469</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="V42" t="n">
-        <v>140.6230303031734</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="W42" t="n">
-        <v>140.6230303031734</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="X42" t="n">
-        <v>10.32</v>
+        <v>293.8254482631224</v>
       </c>
       <c r="Y42" t="n">
-        <v>10.32</v>
+        <v>293.8254482631224</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>145.2949752609077</v>
+        <v>203.3733311394362</v>
       </c>
       <c r="C43" t="n">
-        <v>117.2896756164182</v>
+        <v>203.3733311394362</v>
       </c>
       <c r="D43" t="n">
-        <v>76.34400081282675</v>
+        <v>162.4276563358448</v>
       </c>
       <c r="E43" t="n">
-        <v>39.99965249266862</v>
+        <v>126.0833080156866</v>
       </c>
       <c r="F43" t="n">
+        <v>126.0833080156866</v>
+      </c>
+      <c r="G43" t="n">
+        <v>126.3897820992932</v>
+      </c>
+      <c r="H43" t="n">
+        <v>145.5673692259039</v>
+      </c>
+      <c r="I43" t="n">
+        <v>223.7729419324786</v>
+      </c>
+      <c r="J43" t="n">
+        <v>351.4829419324948</v>
+      </c>
+      <c r="K43" t="n">
+        <v>351.4829419324948</v>
+      </c>
+      <c r="L43" t="n">
+        <v>224.2098616605205</v>
+      </c>
+      <c r="M43" t="n">
+        <v>93.90683135729583</v>
+      </c>
+      <c r="N43" t="n">
         <v>10.32</v>
       </c>
-      <c r="G43" t="n">
-        <v>10.62647408360658</v>
-      </c>
-      <c r="H43" t="n">
-        <v>29.80406121021726</v>
-      </c>
-      <c r="I43" t="n">
-        <v>108.009633916792</v>
-      </c>
-      <c r="J43" t="n">
-        <v>235.7196339168082</v>
-      </c>
-      <c r="K43" t="n">
-        <v>233.2376468018931</v>
-      </c>
-      <c r="L43" t="n">
-        <v>233.2376468018931</v>
-      </c>
-      <c r="M43" t="n">
-        <v>152.4807727435902</v>
-      </c>
-      <c r="N43" t="n">
-        <v>152.4807727435902</v>
-      </c>
       <c r="O43" t="n">
-        <v>152.4807727435902</v>
+        <v>10.32</v>
       </c>
       <c r="P43" t="n">
-        <v>152.4807727435902</v>
+        <v>10.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>152.4807727435902</v>
+        <v>10.32</v>
       </c>
       <c r="R43" t="n">
-        <v>152.4807727435902</v>
+        <v>10.32</v>
       </c>
       <c r="S43" t="n">
-        <v>40.14346090596504</v>
+        <v>10.32</v>
       </c>
       <c r="T43" t="n">
-        <v>76.26420235985186</v>
+        <v>46.44074145388683</v>
       </c>
       <c r="U43" t="n">
-        <v>169.3844808997779</v>
+        <v>139.5610199938128</v>
       </c>
       <c r="V43" t="n">
-        <v>214.7558737857238</v>
+        <v>184.9324128797588</v>
       </c>
       <c r="W43" t="n">
-        <v>233.1967920454012</v>
+        <v>203.3733311394362</v>
       </c>
       <c r="X43" t="n">
-        <v>230.7284633281209</v>
+        <v>203.3733311394362</v>
       </c>
       <c r="Y43" t="n">
-        <v>187.8341675205832</v>
+        <v>203.3733311394362</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>500</v>
+        <v>262.5252525253234</v>
       </c>
       <c r="C44" t="n">
-        <v>500</v>
+        <v>262.5252525253234</v>
       </c>
       <c r="D44" t="n">
-        <v>373.7373737373379</v>
+        <v>262.5252525253234</v>
       </c>
       <c r="E44" t="n">
-        <v>373.7373737373379</v>
+        <v>136.2626262626617</v>
       </c>
       <c r="F44" t="n">
-        <v>247.4747474746757</v>
+        <v>10</v>
       </c>
       <c r="G44" t="n">
-        <v>136.2626262626621</v>
+        <v>10</v>
       </c>
       <c r="H44" t="n">
         <v>10</v>
@@ -7642,22 +7642,22 @@
         <v>41.51406683243596</v>
       </c>
       <c r="K44" t="n">
-        <v>140.7406624103254</v>
+        <v>165.264066832436</v>
       </c>
       <c r="L44" t="n">
-        <v>263.8400284404761</v>
+        <v>288.3634328625867</v>
       </c>
       <c r="M44" t="n">
-        <v>263.8400284404761</v>
+        <v>326.2245487608371</v>
       </c>
       <c r="N44" t="n">
-        <v>263.8400284404761</v>
+        <v>326.2245487608371</v>
       </c>
       <c r="O44" t="n">
-        <v>325.7260226877528</v>
+        <v>388.1105430081138</v>
       </c>
       <c r="P44" t="n">
-        <v>449.4760226877879</v>
+        <v>500</v>
       </c>
       <c r="Q44" t="n">
         <v>500</v>
@@ -7669,22 +7669,22 @@
         <v>500</v>
       </c>
       <c r="T44" t="n">
-        <v>500</v>
+        <v>373.7373737373383</v>
       </c>
       <c r="U44" t="n">
-        <v>500</v>
+        <v>373.7373737373383</v>
       </c>
       <c r="V44" t="n">
-        <v>500</v>
+        <v>373.7373737373383</v>
       </c>
       <c r="W44" t="n">
-        <v>500</v>
+        <v>262.5252525253234</v>
       </c>
       <c r="X44" t="n">
-        <v>500</v>
+        <v>262.5252525253234</v>
       </c>
       <c r="Y44" t="n">
-        <v>500</v>
+        <v>262.5252525253234</v>
       </c>
     </row>
     <row r="45">
@@ -7694,19 +7694,19 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>105.5921639776534</v>
+        <v>186.7214073810544</v>
       </c>
       <c r="C45" t="n">
-        <v>105.5921639776534</v>
+        <v>186.7214073810544</v>
       </c>
       <c r="D45" t="n">
-        <v>105.5921639776534</v>
+        <v>186.7214073810544</v>
       </c>
       <c r="E45" t="n">
-        <v>105.5921639776534</v>
+        <v>186.7214073810544</v>
       </c>
       <c r="F45" t="n">
-        <v>10</v>
+        <v>91.12924340340098</v>
       </c>
       <c r="G45" t="n">
         <v>10</v>
@@ -7721,7 +7721,7 @@
         <v>133.75</v>
       </c>
       <c r="K45" t="n">
-        <v>133.75</v>
+        <v>252.5</v>
       </c>
       <c r="L45" t="n">
         <v>252.5</v>
@@ -7742,28 +7742,28 @@
         <v>500</v>
       </c>
       <c r="R45" t="n">
-        <v>500</v>
+        <v>373.7373737369861</v>
       </c>
       <c r="S45" t="n">
-        <v>500</v>
+        <v>373.7373737369861</v>
       </c>
       <c r="T45" t="n">
-        <v>373.7373737370356</v>
+        <v>312.9840336439996</v>
       </c>
       <c r="U45" t="n">
-        <v>373.7373737370356</v>
+        <v>312.9840336439996</v>
       </c>
       <c r="V45" t="n">
-        <v>247.4747474741027</v>
+        <v>312.9840336439996</v>
       </c>
       <c r="W45" t="n">
-        <v>247.4747474741027</v>
+        <v>312.9840336439996</v>
       </c>
       <c r="X45" t="n">
-        <v>247.4747474741027</v>
+        <v>312.9840336439996</v>
       </c>
       <c r="Y45" t="n">
-        <v>231.8547902405858</v>
+        <v>312.9840336439996</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>144.9749752609077</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="C46" t="n">
-        <v>116.9696756164182</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="D46" t="n">
-        <v>76.02400081282676</v>
+        <v>162.1076563358448</v>
       </c>
       <c r="E46" t="n">
-        <v>39.67965249266862</v>
+        <v>125.7633080156866</v>
       </c>
       <c r="F46" t="n">
+        <v>96.08365552301802</v>
+      </c>
+      <c r="G46" t="n">
+        <v>96.3901296066246</v>
+      </c>
+      <c r="H46" t="n">
+        <v>115.5677167332353</v>
+      </c>
+      <c r="I46" t="n">
+        <v>193.77328943981</v>
+      </c>
+      <c r="J46" t="n">
+        <v>317.52328943981</v>
+      </c>
+      <c r="K46" t="n">
+        <v>317.52328943981</v>
+      </c>
+      <c r="L46" t="n">
+        <v>317.52328943981</v>
+      </c>
+      <c r="M46" t="n">
+        <v>262.5252525252525</v>
+      </c>
+      <c r="N46" t="n">
+        <v>262.5252525252525</v>
+      </c>
+      <c r="O46" t="n">
+        <v>262.5252525252525</v>
+      </c>
+      <c r="P46" t="n">
+        <v>136.2626262626263</v>
+      </c>
+      <c r="Q46" t="n">
         <v>10</v>
       </c>
-      <c r="G46" t="n">
-        <v>10.30647408360657</v>
-      </c>
-      <c r="H46" t="n">
-        <v>29.48406121021726</v>
-      </c>
-      <c r="I46" t="n">
-        <v>107.689633916792</v>
-      </c>
-      <c r="J46" t="n">
-        <v>231.439633916792</v>
-      </c>
-      <c r="K46" t="n">
-        <v>228.9576468018768</v>
-      </c>
-      <c r="L46" t="n">
-        <v>102.6950205392505</v>
-      </c>
-      <c r="M46" t="n">
-        <v>37.3551321886847</v>
-      </c>
-      <c r="N46" t="n">
-        <v>37.3551321886847</v>
-      </c>
-      <c r="O46" t="n">
-        <v>37.3551321886847</v>
-      </c>
-      <c r="P46" t="n">
-        <v>37.3551321886847</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>37.3551321886847</v>
-      </c>
       <c r="R46" t="n">
-        <v>37.3551321886847</v>
+        <v>10</v>
       </c>
       <c r="S46" t="n">
-        <v>37.3551321886847</v>
+        <v>10</v>
       </c>
       <c r="T46" t="n">
-        <v>73.47587364257153</v>
+        <v>46.12074145388683</v>
       </c>
       <c r="U46" t="n">
-        <v>166.5961521824975</v>
+        <v>139.2410199938128</v>
       </c>
       <c r="V46" t="n">
-        <v>211.9675450684435</v>
+        <v>184.6124128797588</v>
       </c>
       <c r="W46" t="n">
-        <v>230.4084633281209</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="X46" t="n">
-        <v>230.4084633281209</v>
+        <v>203.0533311394362</v>
       </c>
       <c r="Y46" t="n">
-        <v>187.5141675205832</v>
+        <v>203.0533311394362</v>
       </c>
     </row>
   </sheetData>
@@ -7967,13 +7967,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>23.77111557788945</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>441.5335604820302</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N2" t="n">
         <v>336.654907818579</v>
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>87.73406121190752</v>
+        <v>147.1319262124245</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8049,16 +8049,16 @@
         <v>36.69966924109012</v>
       </c>
       <c r="L3" t="n">
-        <v>22.46041394129978</v>
+        <v>146.4604139412998</v>
       </c>
       <c r="M3" t="n">
-        <v>396.9146772555022</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N3" t="n">
         <v>241.1347695155256</v>
       </c>
       <c r="O3" t="n">
-        <v>164.9190033132516</v>
+        <v>159.9089023031507</v>
       </c>
       <c r="P3" t="n">
         <v>148.9804809108019</v>
@@ -8210,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>465.3046760599197</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N5" t="n">
-        <v>336.654907818579</v>
+        <v>396.0527728190959</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8280,13 +8280,13 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J6" t="n">
-        <v>62.42560738822591</v>
+        <v>181.4155063781249</v>
       </c>
       <c r="K6" t="n">
         <v>36.69966924109012</v>
       </c>
       <c r="L6" t="n">
-        <v>141.4503129311988</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M6" t="n">
         <v>401.9247782656032</v>
@@ -8447,16 +8447,16 @@
         <v>138.6572060301507</v>
       </c>
       <c r="M8" t="n">
-        <v>450.9173988658687</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N8" t="n">
-        <v>599.654907818579</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>200.4888946997206</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>107.5216931067453</v>
       </c>
       <c r="Q8" t="n">
         <v>87.73406121190752</v>
@@ -8520,19 +8520,19 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K9" t="n">
-        <v>192.8640411455174</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L9" t="n">
-        <v>285.4604139412998</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M9" t="n">
-        <v>277.9247782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N9" t="n">
-        <v>241.1347695155256</v>
+        <v>470.3485276335254</v>
       </c>
       <c r="O9" t="n">
-        <v>303.9190033132517</v>
+        <v>40.91900331325166</v>
       </c>
       <c r="P9" t="n">
         <v>219.1507118405495</v>
@@ -8678,10 +8678,10 @@
         <v>292.1676092601657</v>
       </c>
       <c r="K11" t="n">
-        <v>223.7711155778895</v>
+        <v>35.14944765954326</v>
       </c>
       <c r="L11" t="n">
-        <v>11.0355381118045</v>
+        <v>199.6572060301507</v>
       </c>
       <c r="M11" t="n">
         <v>729.9068110594028</v>
@@ -8754,16 +8754,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J12" t="n">
-        <v>65.12066754724033</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K12" t="n">
-        <v>36.69966924109012</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L12" t="n">
-        <v>346.4604139412998</v>
+        <v>118.7058101033326</v>
       </c>
       <c r="M12" t="n">
-        <v>471.6948204301074</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N12" t="n">
         <v>485.4085271713503</v>
@@ -8915,13 +8915,13 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>223.7711155778894</v>
+        <v>3.317056919708953</v>
       </c>
       <c r="L14" t="n">
         <v>199.6572060301507</v>
       </c>
       <c r="M14" t="n">
-        <v>509.4527524012224</v>
+        <v>729.9068110594028</v>
       </c>
       <c r="N14" t="n">
         <v>660.654907818579</v>
@@ -8991,16 +8991,16 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J15" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K15" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L15" t="n">
-        <v>284.1451334081385</v>
+        <v>118.7058101033326</v>
       </c>
       <c r="M15" t="n">
-        <v>471.6948204301074</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N15" t="n">
         <v>485.4085271713503</v>
@@ -9009,7 +9009,7 @@
         <v>364.9190033132517</v>
       </c>
       <c r="P15" t="n">
-        <v>24.9804809108019</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q15" t="n">
         <v>17.27519534353338</v>
@@ -9152,22 +9152,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>202.9742629498597</v>
+        <v>223.7711155778894</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>199.6572060301507</v>
       </c>
       <c r="M17" t="n">
-        <v>729.9068110594028</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N17" t="n">
-        <v>660.654907818579</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>216.5655948689773</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>210.9803464728422</v>
       </c>
       <c r="Q17" t="n">
         <v>87.73406121190752</v>
@@ -9231,22 +9231,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K18" t="n">
-        <v>36.69966924109012</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L18" t="n">
-        <v>184.1163395607517</v>
+        <v>346.4604139412998</v>
       </c>
       <c r="M18" t="n">
-        <v>471.6948204301074</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N18" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O18" t="n">
-        <v>364.9190033132517</v>
+        <v>331.334630405032</v>
       </c>
       <c r="P18" t="n">
-        <v>219.1507118405495</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q18" t="n">
         <v>17.27519534353338</v>
@@ -9386,7 +9386,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>296.1676092601662</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>227.7711155778894</v>
@@ -9395,10 +9395,10 @@
         <v>203.6572060301507</v>
       </c>
       <c r="M20" t="n">
-        <v>545.1235269794397</v>
+        <v>513.2911362396057</v>
       </c>
       <c r="N20" t="n">
-        <v>336.654907818579</v>
+        <v>664.6549078185794</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -9471,19 +9471,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L21" t="n">
-        <v>22.46041394129978</v>
+        <v>350.4604139413003</v>
       </c>
       <c r="M21" t="n">
-        <v>471.6948204301074</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N21" t="n">
-        <v>485.4085271713503</v>
+        <v>265.492307171766</v>
       </c>
       <c r="O21" t="n">
-        <v>368.9190033132517</v>
+        <v>368.9190033132522</v>
       </c>
       <c r="P21" t="n">
-        <v>133.4644496764619</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q21" t="n">
         <v>17.27519534353338</v>
@@ -9626,10 +9626,10 @@
         <v>367.1676092601664</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>95.79600418654658</v>
       </c>
       <c r="L23" t="n">
-        <v>45.28745595966825</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>405.9068110594027</v>
@@ -9638,10 +9638,10 @@
         <v>336.654907818579</v>
       </c>
       <c r="O23" t="n">
-        <v>336.4888946997212</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>285.9803464728429</v>
       </c>
       <c r="Q23" t="n">
         <v>486.7340612119082</v>
@@ -9702,7 +9702,7 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J24" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K24" t="n">
         <v>295.8802408630135</v>
@@ -9714,10 +9714,10 @@
         <v>471.6948204301074</v>
       </c>
       <c r="N24" t="n">
-        <v>485.4085271713503</v>
+        <v>301.4618601324254</v>
       </c>
       <c r="O24" t="n">
-        <v>363.7742663015414</v>
+        <v>382.6817988009037</v>
       </c>
       <c r="P24" t="n">
         <v>219.1507118405495</v>
@@ -9860,28 +9860,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>296.1676092601658</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>227.7711155778894</v>
       </c>
       <c r="L26" t="n">
-        <v>14.87392195018833</v>
+        <v>203.6572060301507</v>
       </c>
       <c r="M26" t="n">
         <v>405.9068110594027</v>
       </c>
       <c r="N26" t="n">
-        <v>664.654907818579</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>214.9803464728423</v>
       </c>
       <c r="Q26" t="n">
-        <v>87.73406121190752</v>
+        <v>308.1380399192685</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -9945,19 +9945,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L27" t="n">
-        <v>22.46041394129978</v>
+        <v>350.4604139412999</v>
       </c>
       <c r="M27" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N27" t="n">
-        <v>485.4085271713503</v>
+        <v>265.8924959370103</v>
       </c>
       <c r="O27" t="n">
-        <v>283.2327411491641</v>
+        <v>368.9190033132518</v>
       </c>
       <c r="P27" t="n">
-        <v>219.1507118405495</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q27" t="n">
         <v>17.27519534353338</v>
@@ -10097,28 +10097,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>296.1676092601667</v>
       </c>
       <c r="K29" t="n">
         <v>227.7711155778894</v>
       </c>
       <c r="L29" t="n">
-        <v>203.6572060301507</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>513.2911362396053</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N29" t="n">
-        <v>664.6549078185799</v>
+        <v>336.654907818579</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>14.87392195018636</v>
       </c>
       <c r="Q29" t="n">
-        <v>87.73406121190752</v>
+        <v>415.7340612119085</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10176,22 +10176,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J30" t="n">
-        <v>227.4647419277884</v>
+        <v>62.42560738822591</v>
       </c>
       <c r="K30" t="n">
-        <v>36.69966924109012</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L30" t="n">
         <v>350.4604139413008</v>
       </c>
       <c r="M30" t="n">
-        <v>471.6948204301074</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N30" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O30" t="n">
-        <v>214.4133127710865</v>
+        <v>314.0419178532299</v>
       </c>
       <c r="P30" t="n">
         <v>219.1507118405495</v>
@@ -10337,10 +10337,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>89.77111557788945</v>
+        <v>64.73119833384726</v>
       </c>
       <c r="L32" t="n">
-        <v>40.61728878610856</v>
+        <v>65.65720603015075</v>
       </c>
       <c r="M32" t="n">
         <v>405.9068110594027</v>
@@ -10413,25 +10413,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J33" t="n">
-        <v>62.42560738822591</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K33" t="n">
         <v>226.6996692410932</v>
       </c>
       <c r="L33" t="n">
-        <v>22.46041394129978</v>
+        <v>212.4604139413028</v>
       </c>
       <c r="M33" t="n">
-        <v>467.9247782656062</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N33" t="n">
-        <v>423.4580018387488</v>
+        <v>431.1347695155287</v>
       </c>
       <c r="O33" t="n">
         <v>40.91900331325166</v>
       </c>
       <c r="P33" t="n">
-        <v>214.9804809108049</v>
+        <v>42.26457869446266</v>
       </c>
       <c r="Q33" t="n">
         <v>17.27519534353338</v>
@@ -10574,16 +10574,16 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>28.77111557788945</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>455.9887463101607</v>
+        <v>405.9068110594027</v>
       </c>
       <c r="N35" t="n">
-        <v>336.654907818579</v>
+        <v>415.5079586472265</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -10656,19 +10656,19 @@
         <v>165.6996692410956</v>
       </c>
       <c r="L36" t="n">
-        <v>151.4604139413053</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M36" t="n">
-        <v>401.7126570534655</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>241.1347695155256</v>
+        <v>370.134769515531</v>
       </c>
       <c r="O36" t="n">
         <v>40.91900331325166</v>
       </c>
       <c r="P36" t="n">
-        <v>24.9804809108019</v>
+        <v>148.7683596986642</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>62.42560738822591</v>
+        <v>191.425607388235</v>
       </c>
       <c r="K39" t="n">
-        <v>36.69966924109012</v>
+        <v>165.6996692410993</v>
       </c>
       <c r="L39" t="n">
-        <v>151.4604139413089</v>
+        <v>146.2482927291512</v>
       </c>
       <c r="M39" t="n">
-        <v>406.9247782656122</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N39" t="n">
-        <v>364.9226483033771</v>
+        <v>241.1347695155256</v>
       </c>
       <c r="O39" t="n">
-        <v>40.91900331325166</v>
+        <v>169.9190033132608</v>
       </c>
       <c r="P39" t="n">
-        <v>153.980480910811</v>
+        <v>24.9804809108019</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11051,10 +11051,10 @@
         <v>28.77111557788945</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4.657206030150746</v>
       </c>
       <c r="M41" t="n">
-        <v>455.9887463101607</v>
+        <v>451.33154028001</v>
       </c>
       <c r="N41" t="n">
         <v>336.654907818579</v>
@@ -11130,19 +11130,19 @@
         <v>165.6996692411065</v>
       </c>
       <c r="L42" t="n">
-        <v>151.4604139413162</v>
+        <v>146.2482927291294</v>
       </c>
       <c r="M42" t="n">
-        <v>406.9247782656195</v>
+        <v>277.9247782656032</v>
       </c>
       <c r="N42" t="n">
         <v>241.1347695155256</v>
       </c>
       <c r="O42" t="n">
-        <v>164.7068821010813</v>
+        <v>169.9190033132681</v>
       </c>
       <c r="P42" t="n">
-        <v>24.9804809108019</v>
+        <v>153.9804809108183</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11285,13 +11285,13 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>24.77111557788945</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>405.9068110594027</v>
+        <v>444.1503624717769</v>
       </c>
       <c r="N44" t="n">
         <v>336.654907818579</v>
@@ -11300,10 +11300,10 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>11.98034647287771</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>138.7683817292935</v>
+        <v>87.73406121190752</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,10 +11364,10 @@
         <v>187.4256073882259</v>
       </c>
       <c r="K45" t="n">
-        <v>36.69966924109012</v>
+        <v>156.6491641905851</v>
       </c>
       <c r="L45" t="n">
-        <v>142.4099088907947</v>
+        <v>22.46041394129978</v>
       </c>
       <c r="M45" t="n">
         <v>277.9247782656032</v>
@@ -22512,22 +22512,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.99931295557451</v>
+        <v>21.79447478477914</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>4.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2.969432588523773</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -22566,19 +22566,19 @@
         <v>76.89299192292594</v>
       </c>
       <c r="T2" t="n">
-        <v>183.2263756984131</v>
+        <v>59.22637569841311</v>
       </c>
       <c r="U2" t="n">
-        <v>125.1582613727313</v>
+        <v>249.1582613727313</v>
       </c>
       <c r="V2" t="n">
-        <v>105.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>116.471708663754</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
-        <v>192.2818334606677</v>
+        <v>68.28183346066771</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -22706,19 +22706,19 @@
         <v>65.22787369763188</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>117.0987146159472</v>
       </c>
       <c r="O4" t="n">
-        <v>66.48805588229362</v>
+        <v>81.26885588229374</v>
       </c>
       <c r="P4" t="n">
         <v>120.7006186397529</v>
       </c>
       <c r="Q4" t="n">
-        <v>296.243266425598</v>
+        <v>172.243266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>194.5895770233278</v>
+        <v>186.7100624073805</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22749,22 +22749,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.969432588523773</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -22800,25 +22800,25 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>76.89299192292592</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>183.2263756984131</v>
       </c>
       <c r="U5" t="n">
-        <v>125.1582613727313</v>
+        <v>249.1582613727313</v>
       </c>
       <c r="V5" t="n">
-        <v>105.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
         <v>114.3734759809475</v>
       </c>
       <c r="X5" t="n">
-        <v>95.28498436407202</v>
+        <v>115.6115267618244</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22940,22 +22940,22 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>65.22787369763188</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>117.0987146159472</v>
       </c>
       <c r="O7" t="n">
-        <v>66.48805588229362</v>
+        <v>81.26885588229374</v>
       </c>
       <c r="P7" t="n">
-        <v>244.7006186397529</v>
+        <v>120.7006186397529</v>
       </c>
       <c r="Q7" t="n">
-        <v>245.3506547391771</v>
+        <v>172.243266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>186.7100624073806</v>
+        <v>186.7100624073805</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -22986,19 +22986,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>31.45319349143467</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.363289606868648</v>
       </c>
       <c r="F8" t="n">
-        <v>1.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -23037,7 +23037,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>73.89299192292592</v>
+        <v>38.98521408211568</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -23046,16 +23046,16 @@
         <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>226.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>189.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>108.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -23180,7 +23180,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>110.8648628356256</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>30.243266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>155.5749252430061</v>
+        <v>44.71006240738057</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23229,7 +23229,7 @@
         <v>141.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>102.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>96.36328960686865</v>
@@ -23238,10 +23238,10 @@
         <v>96.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>94.96943258852377</v>
+        <v>94.96943258852374</v>
       </c>
       <c r="H11" t="n">
-        <v>91.94017126634151</v>
+        <v>91.94017126634148</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,25 +23274,25 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>168.8929919229259</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>341.1582613727313</v>
+        <v>17.15826137271779</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>225.5856569696281</v>
+        <v>330.3734759809475</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>203.3174326828064</v>
+        <v>151.2974660087246</v>
       </c>
     </row>
     <row r="12">
@@ -23350,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.748556743254028</v>
+        <v>1.748556743253999</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -23411,10 +23411,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>63.00034946925458</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>39.43544419587278</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -23423,16 +23423,16 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>163.350351024129</v>
+        <v>12.7006186397529</v>
       </c>
       <c r="Q13" t="n">
-        <v>388.243266425598</v>
+        <v>64.24326642559799</v>
       </c>
       <c r="R13" t="n">
-        <v>78.71006240738058</v>
+        <v>402.7100624073806</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>48.21393871924888</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>102.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -23478,7 +23478,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>91.94017126634148</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23511,10 +23511,10 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>168.8929919229259</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>185.3353002779768</v>
+        <v>40.62727667441106</v>
       </c>
       <c r="U14" t="n">
         <v>341.1582613727313</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>6.373475980947546</v>
+        <v>330.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>284.2818334606677</v>
@@ -23587,7 +23587,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.748556743253999</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -23602,7 +23602,7 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.748556743249836</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -23654,22 +23654,22 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>209.0987146159472</v>
       </c>
       <c r="O16" t="n">
-        <v>282.4880558822936</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>156.6483564225866</v>
+        <v>12.7006186397529</v>
       </c>
       <c r="Q16" t="n">
         <v>64.24326642559799</v>
       </c>
       <c r="R16" t="n">
-        <v>78.71006240738058</v>
+        <v>344.2610801758096</v>
       </c>
       <c r="S16" t="n">
-        <v>48.21393871924888</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23697,13 +23697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86.99931295557451</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>54.47457824299391</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>15.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -23757,16 +23757,16 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>4.32428841253224</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>243.3734759809475</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>90.88471745506165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -23934,25 +23934,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>73.29562506741968</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>15.33915573984979</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>9.363289606868648</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>9.889628708011855</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>7.969432588523773</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4.940171266341508</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>29.95255966647086</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24000,10 +24000,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>197.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>116.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -24414,10 +24414,10 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>103.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -24459,13 +24459,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>169.8929919229259</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>276.2263756984131</v>
       </c>
       <c r="U26" t="n">
-        <v>117.0615142796023</v>
+        <v>342.1582613727313</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -24474,10 +24474,10 @@
         <v>331.3734759809475</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>143.1378113796221</v>
       </c>
       <c r="Y26" t="n">
-        <v>204.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24599,22 +24599,22 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>158.2278736976318</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>210.0987146159472</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>109.2244790666002</v>
       </c>
       <c r="P28" t="n">
-        <v>337.7006186397529</v>
+        <v>9.700618639739332</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.24326642558526</v>
+        <v>61.24326642558572</v>
       </c>
       <c r="R28" t="n">
-        <v>225.261129787538</v>
+        <v>75.71006240737188</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24648,22 +24648,22 @@
         <v>174.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>142.4745782429939</v>
+        <v>116.2728804137197</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>97.36328960686865</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>97.88962870801186</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>95.96943258852374</v>
       </c>
       <c r="H29" t="n">
-        <v>92.94017126634148</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24702,16 +24702,16 @@
         <v>276.2263756984131</v>
       </c>
       <c r="U29" t="n">
-        <v>313.0453074228978</v>
+        <v>14.15826137270756</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.373475980928902</v>
+        <v>331.3734759809475</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>285.2818334606677</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
@@ -24772,7 +24772,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.225356743242827</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.225356743253997</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>64.00034946925459</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24842,16 +24842,16 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>283.4880558822936</v>
       </c>
       <c r="P31" t="n">
-        <v>9.700618639726372</v>
+        <v>9.700618639725917</v>
       </c>
       <c r="Q31" t="n">
-        <v>97.58004561726568</v>
+        <v>61.24326642556889</v>
       </c>
       <c r="R31" t="n">
-        <v>403.7100624073806</v>
+        <v>220.5591351860389</v>
       </c>
       <c r="S31" t="n">
         <v>49.21393871924888</v>
@@ -24936,16 +24936,16 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
         <v>105.7487082408905</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>0.1632628357445469</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25085,10 +25085,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>41.40652926127905</v>
+        <v>41.2432664255382</v>
       </c>
       <c r="R34" t="n">
-        <v>55.71006240732504</v>
+        <v>55.7100624073214</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25119,7 +25119,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -25170,22 +25170,22 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>11.89299192292594</v>
       </c>
       <c r="T35" t="n">
-        <v>118.2263756984131</v>
+        <v>50.92060838144073</v>
       </c>
       <c r="U35" t="n">
-        <v>55.15826137265867</v>
+        <v>55.1582613726514</v>
       </c>
       <c r="V35" t="n">
-        <v>124.7193951889321</v>
+        <v>35.85102416675079</v>
       </c>
       <c r="W35" t="n">
-        <v>44.37347598088661</v>
+        <v>44.37347598087933</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>127.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>0</v>
@@ -25319,13 +25319,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>50.70061863967567</v>
+        <v>50.70061863966475</v>
       </c>
       <c r="Q37" t="n">
-        <v>102.2432664255248</v>
+        <v>166.2068369240086</v>
       </c>
       <c r="R37" t="n">
-        <v>180.6736329057718</v>
+        <v>116.7100624072989</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -25356,7 +25356,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>16.99931295557451</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
@@ -25407,25 +25407,25 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>11.89299192292592</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>118.2263756984131</v>
       </c>
       <c r="U38" t="n">
-        <v>133.2530080931925</v>
+        <v>55.15826137262184</v>
       </c>
       <c r="V38" t="n">
-        <v>35.85102416675034</v>
+        <v>49.50965762769452</v>
       </c>
       <c r="W38" t="n">
-        <v>173.3734759809475</v>
+        <v>44.3734759808541</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>46.31743268280638</v>
       </c>
     </row>
     <row r="39">
@@ -25547,7 +25547,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.2278736976318569</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -25556,13 +25556,13 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>50.7006186396427</v>
+        <v>50.70061863963542</v>
       </c>
       <c r="Q40" t="n">
-        <v>102.2432664254916</v>
+        <v>166.4347106216919</v>
       </c>
       <c r="R40" t="n">
-        <v>180.673632905838</v>
+        <v>116.7100624072768</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>236.9993129555745</v>
+        <v>107.9993129555581</v>
       </c>
       <c r="C41" t="n">
         <v>204.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>51.71595574020525</v>
+        <v>36.33915573983336</v>
       </c>
       <c r="E41" t="n">
         <v>159.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>30.88962870799548</v>
+        <v>159.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>157.9694325885237</v>
       </c>
       <c r="H41" t="n">
-        <v>25.94017126617024</v>
+        <v>154.9401712663415</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,7 +25644,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>102.8929919227581</v>
+        <v>102.8929919227438</v>
       </c>
       <c r="T41" t="n">
         <v>338.2263756984131</v>
@@ -25659,7 +25659,7 @@
         <v>393.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>347.2818334606677</v>
+        <v>233.6586334608826</v>
       </c>
       <c r="Y41" t="n">
         <v>266.3174326828064</v>
@@ -25678,19 +25678,19 @@
         <v>116.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>102.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>97.67209722191262</v>
       </c>
       <c r="F42" t="n">
-        <v>94.63624233787687</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>80.31795096936696</v>
       </c>
       <c r="H42" t="n">
-        <v>83.0964645449117</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,25 +25720,25 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>147.0985520091863</v>
+        <v>276.0985520093604</v>
       </c>
       <c r="S42" t="n">
-        <v>100.1100452480878</v>
+        <v>213.7332452476302</v>
       </c>
       <c r="T42" t="n">
-        <v>158.6584821986459</v>
+        <v>67.70567597931769</v>
       </c>
       <c r="U42" t="n">
-        <v>155.1826239111302</v>
+        <v>26.18262391094953</v>
       </c>
       <c r="V42" t="n">
-        <v>40.51066719137845</v>
+        <v>169.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>187.3731429098285</v>
       </c>
       <c r="X42" t="n">
-        <v>45.86273944524584</v>
+        <v>174.8627394453875</v>
       </c>
       <c r="Y42" t="n">
         <v>154.3913927661343</v>
@@ -25751,10 +25751,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>42.11380033707866</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>27.72524664804467</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -25763,7 +25763,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>29.38285596774193</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -25778,16 +25778,16 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>2.457167243766001</v>
       </c>
       <c r="L43" t="n">
-        <v>126.0003494692546</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>140.278568379912</v>
+        <v>91.22787369743941</v>
       </c>
       <c r="N43" t="n">
-        <v>272.0987146159472</v>
+        <v>189.3477515722243</v>
       </c>
       <c r="O43" t="n">
         <v>345.4880558822936</v>
@@ -25802,7 +25802,7 @@
         <v>465.7100624073806</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>111.2139387192489</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25817,10 +25817,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.443645430107551</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
     <row r="44">
@@ -25836,19 +25836,19 @@
         <v>204.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>40.33915573981426</v>
+        <v>165.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>159.3632896068686</v>
+        <v>34.36328960683363</v>
       </c>
       <c r="F44" t="n">
-        <v>34.88962870797639</v>
+        <v>34.88962870797684</v>
       </c>
       <c r="G44" t="n">
-        <v>47.86943258863033</v>
+        <v>157.9694325885238</v>
       </c>
       <c r="H44" t="n">
-        <v>29.94017126630598</v>
+        <v>154.9401712663415</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25884,7 +25884,7 @@
         <v>231.8929919229259</v>
       </c>
       <c r="T44" t="n">
-        <v>338.2263756984131</v>
+        <v>213.2263756983781</v>
       </c>
       <c r="U44" t="n">
         <v>404.1582613727313</v>
@@ -25893,7 +25893,7 @@
         <v>384.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>393.3734759809475</v>
+        <v>283.2734759810528</v>
       </c>
       <c r="X44" t="n">
         <v>347.2818334606677</v>
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14.55655664602358</v>
+        <v>14.55655664601085</v>
       </c>
       <c r="C45" t="n">
         <v>116.0999124455193</v>
@@ -25924,7 +25924,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>80.31795096936696</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>83.09646454491173</v>
@@ -25957,19 +25957,19 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>276.0985520093604</v>
+        <v>151.0985520089766</v>
       </c>
       <c r="S45" t="n">
         <v>213.7332452476302</v>
       </c>
       <c r="T45" t="n">
-        <v>33.65848219831111</v>
+        <v>98.51267550658935</v>
       </c>
       <c r="U45" t="n">
         <v>155.1826239111301</v>
       </c>
       <c r="V45" t="n">
-        <v>44.51066719121667</v>
+        <v>169.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>187.3731429098285</v>
@@ -25978,7 +25978,7 @@
         <v>174.8627394453875</v>
       </c>
       <c r="Y45" t="n">
-        <v>138.9276351049525</v>
+        <v>154.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -25988,10 +25988,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>42.11380033707866</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>27.72524664804467</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -26015,13 +26015,13 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2.457167243766008</v>
       </c>
       <c r="L46" t="n">
-        <v>1.000349469254587</v>
+        <v>126.0003494692546</v>
       </c>
       <c r="M46" t="n">
-        <v>155.5413842305717</v>
+        <v>165.77981715222</v>
       </c>
       <c r="N46" t="n">
         <v>272.0987146159472</v>
@@ -26030,10 +26030,10 @@
         <v>345.4880558822937</v>
       </c>
       <c r="P46" t="n">
-        <v>399.7006186397529</v>
+        <v>274.7006186397529</v>
       </c>
       <c r="Q46" t="n">
-        <v>451.243266425598</v>
+        <v>326.243266425598</v>
       </c>
       <c r="R46" t="n">
         <v>465.7100624073805</v>
@@ -26057,7 +26057,7 @@
         <v>2.443645430107551</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>42.46535284946236</v>
       </c>
     </row>
   </sheetData>
@@ -26102,7 +26102,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2858238.70528147</v>
+        <v>2858238.705281469</v>
       </c>
     </row>
     <row r="5">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3745316.201342963</v>
+        <v>3745316.201342962</v>
       </c>
     </row>
     <row r="6">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5579870.13766769</v>
+        <v>5579870.137667689</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6542434.02232074</v>
+        <v>6542434.022320739</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7533885.337669406</v>
+        <v>7533885.337669405</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8392493.027459973</v>
+        <v>8392493.027459972</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9266534.826341452</v>
+        <v>9266534.82634145</v>
       </c>
     </row>
     <row r="12">
@@ -26269,7 +26269,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1136467.034156638</v>
+        <v>1136467.034156637</v>
       </c>
       <c r="C2" t="n">
         <v>1136467.034156637</v>
@@ -26299,7 +26299,7 @@
         <v>1099600.972786379</v>
       </c>
       <c r="L2" t="n">
-        <v>1217412.92883266</v>
+        <v>1217412.928832659</v>
       </c>
       <c r="M2" t="n">
         <v>1193500.95274466</v>
@@ -26308,10 +26308,10 @@
         <v>1193500.952744659</v>
       </c>
       <c r="O2" t="n">
-        <v>865040.9198157447</v>
+        <v>865040.9198157449</v>
       </c>
       <c r="P2" t="n">
-        <v>863102.6978157446</v>
+        <v>863102.6978157444</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>582227.2078207359</v>
+        <v>582219.8413731204</v>
       </c>
       <c r="C4" t="n">
-        <v>580188.050071653</v>
+        <v>580180.6836240374</v>
       </c>
       <c r="D4" t="n">
-        <v>605717.0639415308</v>
+        <v>605706.6050732387</v>
       </c>
       <c r="E4" t="n">
-        <v>545838.6133645035</v>
+        <v>545826.7968390246</v>
       </c>
       <c r="F4" t="n">
-        <v>544096.6128081323</v>
+        <v>544084.7962826535</v>
       </c>
       <c r="G4" t="n">
-        <v>605315.9923374224</v>
+        <v>605304.1758119436</v>
       </c>
       <c r="H4" t="n">
-        <v>603835.1295023952</v>
+        <v>603823.2239502155</v>
       </c>
       <c r="I4" t="n">
-        <v>609265.007141853</v>
+        <v>609251.5213657346</v>
       </c>
       <c r="J4" t="n">
-        <v>537112.7865549482</v>
+        <v>537100.8810027686</v>
       </c>
       <c r="K4" t="n">
-        <v>535362.3027345806</v>
+        <v>535350.3971824013</v>
       </c>
       <c r="L4" t="n">
-        <v>604981.3622014383</v>
+        <v>604972.5280704354</v>
       </c>
       <c r="M4" t="n">
-        <v>591480.7049964441</v>
+        <v>591473.2285226278</v>
       </c>
       <c r="N4" t="n">
-        <v>589279.0104119544</v>
+        <v>589271.5339381382</v>
       </c>
       <c r="O4" t="n">
-        <v>404184.9363094252</v>
+        <v>404177.459835609</v>
       </c>
       <c r="P4" t="n">
-        <v>401819.8426883493</v>
+        <v>401812.4552412339</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>274052.2263359021</v>
+        <v>274059.5927835169</v>
       </c>
       <c r="C6" t="n">
-        <v>510839.3840849843</v>
+        <v>510846.7505326001</v>
       </c>
       <c r="D6" t="n">
-        <v>483212.5263903023</v>
+        <v>483222.9852585946</v>
       </c>
       <c r="E6" t="n">
-        <v>238142.5540207753</v>
+        <v>238154.3705462544</v>
       </c>
       <c r="F6" t="n">
-        <v>505356.5545771468</v>
+        <v>505368.3711026256</v>
       </c>
       <c r="G6" t="n">
-        <v>476573.5434922794</v>
+        <v>476585.360017758</v>
       </c>
       <c r="H6" t="n">
-        <v>547207.9618793066</v>
+        <v>547219.867431487</v>
       </c>
       <c r="I6" t="n">
-        <v>532148.5591824271</v>
+        <v>532162.0449585455</v>
       </c>
       <c r="J6" t="n">
-        <v>317807.8032314301</v>
+        <v>317819.7087836097</v>
       </c>
       <c r="K6" t="n">
-        <v>514214.2870517982</v>
+        <v>514226.1926039773</v>
       </c>
       <c r="L6" t="n">
-        <v>361162.6816312214</v>
+        <v>361171.5157622241</v>
       </c>
       <c r="M6" t="n">
-        <v>550812.1627482155</v>
+        <v>550819.6392220317</v>
       </c>
       <c r="N6" t="n">
-        <v>553013.8573327049</v>
+        <v>553021.3338065211</v>
       </c>
       <c r="O6" t="n">
-        <v>428143.0785063196</v>
+        <v>428150.5549801359</v>
       </c>
       <c r="P6" t="n">
-        <v>428813.1501273952</v>
+        <v>428820.5375745105</v>
       </c>
     </row>
   </sheetData>
@@ -26975,7 +26975,7 @@
         <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
@@ -26984,7 +26984,7 @@
         <v>305</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>87</v>
@@ -27533,7 +27533,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I3" t="n">
-        <v>202.6112915517259</v>
+        <v>91.07586615948195</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27563,10 +27563,10 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>334.7332452476302</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>353.7313293601259</v>
+        <v>400</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27591,10 +27591,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
-        <v>272.7252466480447</v>
+        <v>396.7252466480447</v>
       </c>
       <c r="D4" t="n">
         <v>285.5362180555555</v>
@@ -27606,22 +27606,22 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G4" t="n">
-        <v>368.6904302185793</v>
+        <v>244.6904302185792</v>
       </c>
       <c r="H4" t="n">
         <v>225.6286998721104</v>
       </c>
       <c r="I4" t="n">
-        <v>290.0044720135609</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J4" t="n">
-        <v>67.59854290876589</v>
+        <v>85.4843931024327</v>
       </c>
       <c r="K4" t="n">
         <v>247.457167243766</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>371.0003494692546</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27654,10 +27654,10 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>226.3728098387097</v>
+        <v>350.3728098387097</v>
       </c>
       <c r="X4" t="n">
-        <v>247.4436454301076</v>
+        <v>371.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>287.4653528494624</v>
@@ -27794,22 +27794,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
+        <v>399.0311035233368</v>
+      </c>
+      <c r="T6" t="n">
+        <v>279.6584821986459</v>
+      </c>
+      <c r="U6" t="n">
         <v>400</v>
       </c>
-      <c r="T6" t="n">
-        <v>400</v>
-      </c>
-      <c r="U6" t="n">
-        <v>288.464574607756</v>
-      </c>
       <c r="V6" t="n">
-        <v>400</v>
+        <v>290.5106671915202</v>
       </c>
       <c r="W6" t="n">
         <v>400</v>
@@ -27828,16 +27828,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>396.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
         <v>274.3828559677419</v>
@@ -27852,13 +27852,13 @@
         <v>166.0044720135609</v>
       </c>
       <c r="J7" t="n">
-        <v>100.2708038524384</v>
+        <v>10.28055539328483</v>
       </c>
       <c r="K7" t="n">
-        <v>371.457167243766</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L7" t="n">
-        <v>400</v>
+        <v>371.0003494692546</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27885,13 +27885,13 @@
         <v>208.5144025718315</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9391125859333</v>
+        <v>171.559934805423</v>
       </c>
       <c r="V7" t="n">
-        <v>323.1703102162162</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>350.3728098387097</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
@@ -27989,16 +27989,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>157.5619546938711</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>79.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>76.63624233787687</v>
       </c>
       <c r="G9" t="n">
         <v>325.317950969367</v>
@@ -28007,7 +28007,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I9" t="n">
-        <v>202.6112915517259</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,10 +28034,10 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>258.0985520093604</v>
+        <v>403</v>
       </c>
       <c r="S9" t="n">
-        <v>195.7332452476302</v>
+        <v>403</v>
       </c>
       <c r="T9" t="n">
         <v>403</v>
@@ -28046,7 +28046,7 @@
         <v>400.1826239111301</v>
       </c>
       <c r="V9" t="n">
-        <v>349.0189534396353</v>
+        <v>403</v>
       </c>
       <c r="W9" t="n">
         <v>403</v>
@@ -28065,19 +28065,19 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C10" t="n">
+        <v>301.3861929116377</v>
+      </c>
+      <c r="D10" t="n">
         <v>403</v>
       </c>
-      <c r="C10" t="n">
-        <v>272.7252466480447</v>
-      </c>
-      <c r="D10" t="n">
-        <v>285.5362180555555</v>
-      </c>
       <c r="E10" t="n">
-        <v>302.8596734682018</v>
+        <v>403</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>403</v>
       </c>
       <c r="G10" t="n">
         <v>244.6904302185792</v>
@@ -28086,7 +28086,7 @@
         <v>225.6286998721104</v>
       </c>
       <c r="I10" t="n">
-        <v>166.0044720135609</v>
+        <v>403</v>
       </c>
       <c r="J10" t="n">
         <v>10.28055539328483</v>
@@ -28125,16 +28125,16 @@
         <v>403</v>
       </c>
       <c r="V10" t="n">
-        <v>403</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>403</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>403</v>
       </c>
       <c r="Y10" t="n">
-        <v>403</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28311,7 +28311,7 @@
         <v>308</v>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F13" t="n">
         <v>308</v>
@@ -28359,7 +28359,7 @@
         <v>308</v>
       </c>
       <c r="U13" t="n">
-        <v>277.6150749880303</v>
+        <v>308</v>
       </c>
       <c r="V13" t="n">
         <v>308</v>
@@ -28371,7 +28371,7 @@
         <v>308</v>
       </c>
       <c r="Y13" t="n">
-        <v>308</v>
+        <v>304.6341701510737</v>
       </c>
     </row>
     <row r="14">
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>119.2643216942573</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R15" t="n">
         <v>308</v>
@@ -28566,7 +28566,7 @@
         <v>308</v>
       </c>
       <c r="K16" t="n">
-        <v>277.6150749880305</v>
+        <v>308</v>
       </c>
       <c r="L16" t="n">
         <v>308</v>
@@ -28605,7 +28605,7 @@
         <v>308</v>
       </c>
       <c r="X16" t="n">
-        <v>308</v>
+        <v>277.6150749880303</v>
       </c>
       <c r="Y16" t="n">
         <v>308</v>
@@ -28700,16 +28700,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>41.53155812515649</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>23.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>18.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>15.63624233787687</v>
       </c>
       <c r="G18" t="n">
         <v>325.317950969367</v>
@@ -28718,7 +28718,7 @@
         <v>328.0964645449117</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R18" t="n">
-        <v>272.860313320233</v>
+        <v>395</v>
       </c>
       <c r="S18" t="n">
         <v>395</v>
@@ -28754,7 +28754,7 @@
         <v>395</v>
       </c>
       <c r="U18" t="n">
-        <v>76.18262391113015</v>
+        <v>395</v>
       </c>
       <c r="V18" t="n">
         <v>395</v>
@@ -28776,34 +28776,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>287.1138003370787</v>
+        <v>395</v>
       </c>
       <c r="C19" t="n">
-        <v>345.1393980890789</v>
+        <v>395</v>
       </c>
       <c r="D19" t="n">
         <v>395</v>
       </c>
       <c r="E19" t="n">
-        <v>280.9809048369565</v>
+        <v>318.9007249561505</v>
       </c>
       <c r="F19" t="n">
-        <v>395</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G19" t="n">
         <v>244.6904302185792</v>
       </c>
       <c r="H19" t="n">
-        <v>395</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I19" t="n">
-        <v>395</v>
+        <v>166.0044720135609</v>
       </c>
       <c r="J19" t="n">
-        <v>334.2805553932848</v>
+        <v>10.28055539328483</v>
       </c>
       <c r="K19" t="n">
-        <v>395</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L19" t="n">
         <v>371.0003494692546</v>
@@ -28827,22 +28827,22 @@
         <v>395</v>
       </c>
       <c r="S19" t="n">
-        <v>356.2139387192489</v>
+        <v>395</v>
       </c>
       <c r="T19" t="n">
         <v>208.5144025718315</v>
       </c>
       <c r="U19" t="n">
-        <v>150.9391125859333</v>
+        <v>395</v>
       </c>
       <c r="V19" t="n">
-        <v>199.1703102162162</v>
+        <v>395</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>395</v>
       </c>
       <c r="X19" t="n">
-        <v>247.4436454301076</v>
+        <v>395</v>
       </c>
       <c r="Y19" t="n">
         <v>395</v>
@@ -28940,16 +28940,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>347.9376868977026</v>
+        <v>19.93768689770214</v>
       </c>
       <c r="E21" t="n">
-        <v>342.6720972219126</v>
+        <v>340.8984938709178</v>
       </c>
       <c r="F21" t="n">
-        <v>339.6362423378769</v>
+        <v>11.63624233787633</v>
       </c>
       <c r="G21" t="n">
-        <v>325.317950969367</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>328.0964645449117</v>
@@ -28979,7 +28979,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>119.2643216942532</v>
       </c>
       <c r="R21" t="n">
         <v>395</v>
@@ -28991,16 +28991,16 @@
         <v>395</v>
       </c>
       <c r="U21" t="n">
-        <v>72.18262391113015</v>
+        <v>395</v>
       </c>
       <c r="V21" t="n">
         <v>395</v>
       </c>
       <c r="W21" t="n">
-        <v>104.3731429098285</v>
+        <v>395</v>
       </c>
       <c r="X21" t="n">
-        <v>144.617000552932</v>
+        <v>395</v>
       </c>
       <c r="Y21" t="n">
         <v>395</v>
@@ -29013,13 +29013,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>395</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C22" t="n">
-        <v>395</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D22" t="n">
-        <v>395</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E22" t="n">
         <v>395</v>
@@ -29034,13 +29034,13 @@
         <v>395</v>
       </c>
       <c r="I22" t="n">
-        <v>296.9110116680347</v>
+        <v>395</v>
       </c>
       <c r="J22" t="n">
-        <v>10.28055539328483</v>
+        <v>338.2805553932853</v>
       </c>
       <c r="K22" t="n">
-        <v>247.457167243766</v>
+        <v>395</v>
       </c>
       <c r="L22" t="n">
         <v>371.0003494692546</v>
@@ -29073,16 +29073,16 @@
         <v>150.9391125859333</v>
       </c>
       <c r="V22" t="n">
-        <v>199.1703102162162</v>
+        <v>220.2542258077679</v>
       </c>
       <c r="W22" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X22" t="n">
-        <v>395</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y22" t="n">
-        <v>395</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="23">
@@ -29113,7 +29113,7 @@
         <v>392</v>
       </c>
       <c r="I23" t="n">
-        <v>118.3418788500341</v>
+        <v>119.704114456554</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>201.3831817428673</v>
+        <v>200.0209461363477</v>
       </c>
       <c r="S23" t="n">
         <v>392</v>
@@ -29171,19 +29171,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>156.717584582649</v>
       </c>
       <c r="G24" t="n">
         <v>325.317950969367</v>
@@ -29234,13 +29234,13 @@
         <v>392</v>
       </c>
       <c r="W24" t="n">
-        <v>304.6740701144436</v>
+        <v>392</v>
       </c>
       <c r="X24" t="n">
-        <v>20.86273944538689</v>
+        <v>392</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.3913927661336913</v>
+        <v>392</v>
       </c>
     </row>
     <row r="25">
@@ -29250,19 +29250,19 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C25" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D25" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E25" t="n">
+        <v>315.1543507655908</v>
+      </c>
+      <c r="F25" t="n">
         <v>392</v>
-      </c>
-      <c r="C25" t="n">
-        <v>392</v>
-      </c>
-      <c r="D25" t="n">
-        <v>392</v>
-      </c>
-      <c r="E25" t="n">
-        <v>392</v>
-      </c>
-      <c r="F25" t="n">
-        <v>274.3828559677419</v>
       </c>
       <c r="G25" t="n">
         <v>244.6904302185792</v>
@@ -29271,10 +29271,10 @@
         <v>225.6286998721104</v>
       </c>
       <c r="I25" t="n">
-        <v>166.0044720135609</v>
+        <v>392</v>
       </c>
       <c r="J25" t="n">
-        <v>10.28055539328483</v>
+        <v>392</v>
       </c>
       <c r="K25" t="n">
         <v>247.457167243766</v>
@@ -29301,13 +29301,13 @@
         <v>392</v>
       </c>
       <c r="S25" t="n">
-        <v>356.2139387192489</v>
+        <v>392</v>
       </c>
       <c r="T25" t="n">
-        <v>216.5666617196604</v>
+        <v>208.5144025718315</v>
       </c>
       <c r="U25" t="n">
-        <v>392</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V25" t="n">
         <v>392</v>
@@ -29319,7 +29319,7 @@
         <v>392</v>
       </c>
       <c r="Y25" t="n">
-        <v>392</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -29690,7 +29690,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>119.2643216942532</v>
+        <v>119.2643216942644</v>
       </c>
       <c r="R30" t="n">
         <v>307</v>
@@ -29888,22 +29888,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>347.9376868977026</v>
+        <v>157.9376868976996</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>152.6720972219096</v>
       </c>
       <c r="F33" t="n">
-        <v>228.3827943472465</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
-        <v>135.3179509693639</v>
+        <v>325.317950969367</v>
       </c>
       <c r="H33" t="n">
-        <v>138.0964645449087</v>
+        <v>328.0964645449117</v>
       </c>
       <c r="I33" t="n">
-        <v>12.61129155172285</v>
+        <v>202.6112915517259</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>119.2643216942532</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>465</v>
@@ -29945,7 +29945,7 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W33" t="n">
-        <v>432.3731429098285</v>
+        <v>250.3840166134483</v>
       </c>
       <c r="X33" t="n">
         <v>419.8627394453875</v>
@@ -29961,13 +29961,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>287.1138003370787</v>
+        <v>465</v>
       </c>
       <c r="C34" t="n">
         <v>272.7252466480447</v>
       </c>
       <c r="D34" t="n">
-        <v>285.5362180555555</v>
+        <v>289.9732507158574</v>
       </c>
       <c r="E34" t="n">
         <v>280.9809048369565</v>
@@ -29979,7 +29979,7 @@
         <v>244.6904302185792</v>
       </c>
       <c r="H34" t="n">
-        <v>415.6286998721135</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I34" t="n">
         <v>166.0044720135609</v>
@@ -29991,7 +29991,7 @@
         <v>247.457167243766</v>
       </c>
       <c r="L34" t="n">
-        <v>465</v>
+        <v>371.0003494692546</v>
       </c>
       <c r="M34" t="n">
         <v>465</v>
@@ -30012,19 +30012,19 @@
         <v>465</v>
       </c>
       <c r="S34" t="n">
-        <v>465</v>
+        <v>356.2139387192489</v>
       </c>
       <c r="T34" t="n">
-        <v>378.0519230835612</v>
+        <v>398.5144025718345</v>
       </c>
       <c r="U34" t="n">
-        <v>340.9391125859364</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V34" t="n">
-        <v>199.1703102162162</v>
+        <v>389.1703102162193</v>
       </c>
       <c r="W34" t="n">
-        <v>226.3728098387097</v>
+        <v>416.3728098387127</v>
       </c>
       <c r="X34" t="n">
         <v>247.4436454301076</v>
@@ -30122,16 +30122,16 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C36" t="n">
-        <v>232.0999124455138</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>213.6720972219072</v>
+        <v>229.0488972219291</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>210.6362423378714</v>
       </c>
       <c r="G36" t="n">
         <v>325.317950969367</v>
@@ -30167,19 +30167,19 @@
         <v>119.2643216942532</v>
       </c>
       <c r="R36" t="n">
-        <v>465</v>
+        <v>392.098552009355</v>
       </c>
       <c r="S36" t="n">
-        <v>329.7332452476247</v>
+        <v>458.7332452476302</v>
       </c>
       <c r="T36" t="n">
         <v>403.6584821986459</v>
       </c>
       <c r="U36" t="n">
-        <v>400.1826239111301</v>
+        <v>271.1826239111247</v>
       </c>
       <c r="V36" t="n">
-        <v>356.9860192008971</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
         <v>432.3731429098285</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>302.1156178441898</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>272.7252466480447</v>
@@ -30207,7 +30207,7 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>409.980904836962</v>
       </c>
       <c r="F37" t="n">
         <v>403.3828559677474</v>
@@ -30225,7 +30225,7 @@
         <v>10.28055539328483</v>
       </c>
       <c r="K37" t="n">
-        <v>376.4571672437715</v>
+        <v>247.457167243766</v>
       </c>
       <c r="L37" t="n">
         <v>371.0003494692546</v>
@@ -30249,13 +30249,13 @@
         <v>465</v>
       </c>
       <c r="S37" t="n">
-        <v>465</v>
+        <v>356.2139387192489</v>
       </c>
       <c r="T37" t="n">
-        <v>208.5144025718315</v>
+        <v>337.514402571837</v>
       </c>
       <c r="U37" t="n">
-        <v>279.9391125859389</v>
+        <v>150.9391125859333</v>
       </c>
       <c r="V37" t="n">
         <v>199.1703102162162</v>
@@ -30267,7 +30267,7 @@
         <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>287.4653528494624</v>
+        <v>411.2532316373247</v>
       </c>
     </row>
     <row r="38">
@@ -30359,10 +30359,10 @@
         <v>255.5565566463175</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>232.0999124455102</v>
       </c>
       <c r="D39" t="n">
-        <v>218.9376868976935</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
@@ -30422,10 +30422,10 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
-        <v>290.8627394453785</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>270.3913927661253</v>
       </c>
     </row>
     <row r="40">
@@ -30438,7 +30438,7 @@
         <v>287.1138003370787</v>
       </c>
       <c r="C40" t="n">
-        <v>272.7252466480447</v>
+        <v>401.7252466480538</v>
       </c>
       <c r="D40" t="n">
         <v>285.5362180555555</v>
@@ -30447,13 +30447,13 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>403.3828559677511</v>
+        <v>324.3850229441059</v>
       </c>
       <c r="G40" t="n">
         <v>244.6904302185792</v>
       </c>
       <c r="H40" t="n">
-        <v>354.6286998721196</v>
+        <v>225.6286998721104</v>
       </c>
       <c r="I40" t="n">
         <v>166.0044720135609</v>
@@ -30486,7 +30486,7 @@
         <v>465</v>
       </c>
       <c r="S40" t="n">
-        <v>356.2139387192489</v>
+        <v>465</v>
       </c>
       <c r="T40" t="n">
         <v>208.5144025718315</v>
@@ -30501,7 +30501,7 @@
         <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>277.2318736872136</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
         <v>416.4653528494715</v>
@@ -34746,13 +34746,13 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K2" t="n">
-        <v>124</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L2" t="n">
         <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>35.62674942262746</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -34764,7 +34764,7 @@
         <v>113.0196535271578</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>59.39786500051702</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34828,16 +34828,16 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
         <v>118.989898989899</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>124</v>
       </c>
       <c r="P3" t="n">
         <v>124</v>
@@ -34877,10 +34877,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -34892,22 +34892,22 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>57.31798751548107</v>
+        <v>75.20383770914788</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>28.99965053074544</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34940,10 +34940,10 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -34989,10 +34989,10 @@
         <v>124</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>59.39786500051696</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>62.51110530027941</v>
@@ -35059,13 +35059,13 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>118.989898989899</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>118.989898989899</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>124</v>
@@ -35114,16 +35114,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -35138,13 +35138,13 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>89.99024845915361</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>28.99965053074542</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35171,13 +35171,13 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>20.62082221948965</v>
       </c>
       <c r="V7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -35226,16 +35226,16 @@
         <v>263</v>
       </c>
       <c r="M8" t="n">
-        <v>45.01058780646592</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>263</v>
       </c>
-      <c r="O8" t="n">
-        <v>62.51110530027941</v>
-      </c>
       <c r="P8" t="n">
-        <v>113.0196535271578</v>
+        <v>220.541346633903</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -35299,19 +35299,19 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K9" t="n">
-        <v>156.1643719044273</v>
+        <v>259.1805716219234</v>
       </c>
       <c r="L9" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>193.7700421645043</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>229.2137581179998</v>
       </c>
       <c r="O9" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>194.1702309297476</v>
@@ -35351,19 +35351,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>115.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>28.66094626359304</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>117.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>21.87876863124529</v>
+        <v>122.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>128.6171440322581</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -35372,7 +35372,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>236.9955279864391</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -35411,16 +35411,16 @@
         <v>252.0608874140667</v>
       </c>
       <c r="V10" t="n">
-        <v>203.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>176.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>155.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>115.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35457,10 +35457,10 @@
         <v>324</v>
       </c>
       <c r="K11" t="n">
-        <v>324.0000000000001</v>
+        <v>135.3783320816538</v>
       </c>
       <c r="L11" t="n">
-        <v>135.3783320816538</v>
+        <v>324</v>
       </c>
       <c r="M11" t="n">
         <v>324</v>
@@ -35533,16 +35533,16 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>2.695060159014417</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>259.1805716219234</v>
       </c>
       <c r="L12" t="n">
-        <v>324</v>
+        <v>96.24539616203282</v>
       </c>
       <c r="M12" t="n">
-        <v>193.7700421645043</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>244.2737576558247</v>
@@ -35597,13 +35597,13 @@
         <v>22.46378194444452</v>
       </c>
       <c r="E13" t="n">
-        <v>27.01909516304346</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>33.61714403225807</v>
       </c>
       <c r="G13" t="n">
-        <v>63.30956978142078</v>
+        <v>63.30956978142079</v>
       </c>
       <c r="H13" t="n">
         <v>82.37130012788958</v>
@@ -35615,7 +35615,7 @@
         <v>297.7194446067152</v>
       </c>
       <c r="K13" t="n">
-        <v>60.54283275623399</v>
+        <v>60.542832756234</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35645,7 +35645,7 @@
         <v>99.48559742816852</v>
       </c>
       <c r="U13" t="n">
-        <v>126.675962402097</v>
+        <v>157.0608874140667</v>
       </c>
       <c r="V13" t="n">
         <v>108.8296897837838</v>
@@ -35657,7 +35657,7 @@
         <v>60.55635456989245</v>
       </c>
       <c r="Y13" t="n">
-        <v>20.53464715053764</v>
+        <v>17.16881730161136</v>
       </c>
     </row>
     <row r="14">
@@ -35694,13 +35694,13 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K14" t="n">
+        <v>103.5459413418195</v>
+      </c>
+      <c r="L14" t="n">
         <v>324</v>
       </c>
-      <c r="L14" t="n">
-        <v>323.9999999999999</v>
-      </c>
       <c r="M14" t="n">
-        <v>103.5459413418196</v>
+        <v>324</v>
       </c>
       <c r="N14" t="n">
         <v>324</v>
@@ -35770,16 +35770,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K15" t="n">
         <v>259.1805716219234</v>
       </c>
       <c r="L15" t="n">
-        <v>261.6847194668387</v>
+        <v>96.24539616203282</v>
       </c>
       <c r="M15" t="n">
-        <v>193.7700421645043</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>244.2737576558247</v>
@@ -35788,10 +35788,10 @@
         <v>324</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>194.1702309297476</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.134066826240583e-12</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35852,7 +35852,7 @@
         <v>297.7194446067152</v>
       </c>
       <c r="K16" t="n">
-        <v>30.15790774426446</v>
+        <v>60.542832756234</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -35891,7 +35891,7 @@
         <v>81.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>60.55635456989245</v>
+        <v>30.17142955792273</v>
       </c>
       <c r="Y16" t="n">
         <v>20.53464715053764</v>
@@ -35931,22 +35931,22 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K17" t="n">
-        <v>303.2031473719703</v>
+        <v>324</v>
       </c>
       <c r="L17" t="n">
-        <v>124.3427939698493</v>
+        <v>323.9999999999999</v>
       </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>279.0767001692568</v>
+      </c>
+      <c r="P17" t="n">
         <v>324</v>
-      </c>
-      <c r="N17" t="n">
-        <v>324</v>
-      </c>
-      <c r="O17" t="n">
-        <v>62.51110530027941</v>
-      </c>
-      <c r="P17" t="n">
-        <v>113.0196535271578</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -36010,22 +36010,22 @@
         <v>165.0391345395625</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>259.1805716219234</v>
       </c>
       <c r="L18" t="n">
-        <v>161.6559256194519</v>
+        <v>324</v>
       </c>
       <c r="M18" t="n">
-        <v>193.7700421645043</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
         <v>244.2737576558247</v>
       </c>
       <c r="O18" t="n">
-        <v>324</v>
+        <v>290.4156270917803</v>
       </c>
       <c r="P18" t="n">
-        <v>194.1702309297476</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -36062,34 +36062,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>107.8861996629213</v>
       </c>
       <c r="C19" t="n">
-        <v>72.41415144103425</v>
+        <v>122.2747533519553</v>
       </c>
       <c r="D19" t="n">
         <v>109.4637819444445</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>37.91982011919393</v>
       </c>
       <c r="F19" t="n">
-        <v>120.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>169.3713001278896</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>228.9955279864391</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>324</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>147.542832756234</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36113,22 +36113,22 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>38.78606128075114</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>244.0608874140667</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>195.8296897837838</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>168.6271901612903</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>147.5563545698924</v>
       </c>
       <c r="Y19" t="n">
         <v>107.5346471505376</v>
@@ -36165,19 +36165,19 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>328.0000000000005</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K20" t="n">
         <v>328</v>
       </c>
       <c r="L20" t="n">
-        <v>328</v>
+        <v>327.9999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>139.2167159200371</v>
+        <v>107.3843251802029</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="O20" t="n">
         <v>62.51110530027941</v>
@@ -36250,19 +36250,19 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="M21" t="n">
-        <v>193.7700421645043</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>244.2737576558247</v>
+        <v>24.35753765624034</v>
       </c>
       <c r="O21" t="n">
-        <v>328</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="P21" t="n">
-        <v>108.48396876566</v>
+        <v>194.1702309297476</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -36299,13 +36299,13 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>107.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>122.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>109.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>114.0190951630435</v>
@@ -36320,13 +36320,13 @@
         <v>169.3713001278896</v>
       </c>
       <c r="I22" t="n">
-        <v>130.9065396544737</v>
+        <v>228.9955279864391</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>328.0000000000005</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>147.542832756234</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36359,16 +36359,16 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>21.08391559155164</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>147.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>107.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -36405,10 +36405,10 @@
         <v>399.0000000000007</v>
       </c>
       <c r="K23" t="n">
-        <v>100.2288844221105</v>
+        <v>196.0248886086571</v>
       </c>
       <c r="L23" t="n">
-        <v>169.6302499295175</v>
+        <v>124.3427939698493</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -36417,10 +36417,10 @@
         <v>0</v>
       </c>
       <c r="O23" t="n">
+        <v>62.51110530027941</v>
+      </c>
+      <c r="P23" t="n">
         <v>399.0000000000007</v>
-      </c>
-      <c r="P23" t="n">
-        <v>113.0196535271578</v>
       </c>
       <c r="Q23" t="n">
         <v>399.0000000000007</v>
@@ -36481,7 +36481,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K24" t="n">
         <v>259.1805716219234</v>
@@ -36493,10 +36493,10 @@
         <v>193.7700421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>244.2737576558247</v>
+        <v>60.32709061689982</v>
       </c>
       <c r="O24" t="n">
-        <v>322.8552629882898</v>
+        <v>341.7627954876521</v>
       </c>
       <c r="P24" t="n">
         <v>194.1702309297476</v>
@@ -36536,19 +36536,19 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>104.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>119.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>106.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>111.0190951630435</v>
+        <v>34.17344592863431</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>117.6171440322581</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -36557,10 +36557,10 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>225.9955279864391</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>381.7194446067152</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -36587,13 +36587,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>35.78606128075114</v>
       </c>
       <c r="T25" t="n">
-        <v>8.052259147828909</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>241.0608874140667</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
         <v>192.8296897837838</v>
@@ -36605,7 +36605,7 @@
         <v>144.5563545698924</v>
       </c>
       <c r="Y25" t="n">
-        <v>104.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -36639,28 +36639,28 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>328.0000000000001</v>
+        <v>31.8323907398343</v>
       </c>
       <c r="K26" t="n">
         <v>328</v>
       </c>
       <c r="L26" t="n">
-        <v>139.2167159200376</v>
+        <v>327.9999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>328.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>62.51110530027941</v>
       </c>
       <c r="P26" t="n">
-        <v>113.0196535271578</v>
+        <v>328.0000000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>220.403978707361</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36724,19 +36724,19 @@
         <v>259.1805716219234</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>328.0000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>193.7700421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>244.2737576558247</v>
+        <v>24.75772642148463</v>
       </c>
       <c r="O27" t="n">
-        <v>242.3137378359124</v>
+        <v>328.0000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>194.1702309297476</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -36876,28 +36876,28 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>31.8323907398343</v>
+        <v>328.000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>328</v>
       </c>
       <c r="L29" t="n">
-        <v>327.9999999999999</v>
+        <v>124.3427939698493</v>
       </c>
       <c r="M29" t="n">
-        <v>107.3843251802025</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>328.000000000001</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>62.51110530027941</v>
       </c>
       <c r="P29" t="n">
-        <v>113.0196535271578</v>
+        <v>127.8935754773441</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>328.000000000001</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36955,28 +36955,28 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>165.0391345395625</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>259.1805716219234</v>
       </c>
       <c r="L30" t="n">
         <v>328.000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>193.7700421645043</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>244.2737576558247</v>
       </c>
       <c r="O30" t="n">
-        <v>173.4943094578348</v>
+        <v>273.1229145399782</v>
       </c>
       <c r="P30" t="n">
         <v>194.1702309297476</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.125384858254381e-11</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,10 +37116,10 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K32" t="n">
+        <v>164.9600827559578</v>
+      </c>
+      <c r="L32" t="n">
         <v>190</v>
-      </c>
-      <c r="L32" t="n">
-        <v>164.9600827559578</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -37192,25 +37192,25 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>165.0391345395625</v>
       </c>
       <c r="K33" t="n">
         <v>190.000000000003</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>190.000000000003</v>
       </c>
-      <c r="N33" t="n">
-        <v>182.3232323232233</v>
-      </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>190.000000000003</v>
+        <v>17.28409778366076</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -37247,13 +37247,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>177.8861996629213</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>4.437032660301941</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -37265,52 +37265,52 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
         <v>190.000000000003</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>93.99965053074544</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>108.7860612807511</v>
-      </c>
-      <c r="T34" t="n">
-        <v>169.5375205117297</v>
-      </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>190.000000000003</v>
       </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>190.000000000003</v>
       </c>
       <c r="X34" t="n">
         <v>0</v>
@@ -37353,16 +37353,16 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K35" t="n">
-        <v>129</v>
+        <v>100.2288844221106</v>
       </c>
       <c r="L35" t="n">
         <v>124.3427939698492</v>
       </c>
       <c r="M35" t="n">
-        <v>50.08193525075798</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>78.85305082864747</v>
       </c>
       <c r="O35" t="n">
         <v>62.51110530027941</v>
@@ -37435,19 +37435,19 @@
         <v>129.0000000000055</v>
       </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>123.7878787878623</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37484,7 +37484,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15.00181750711117</v>
+        <v>0</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
@@ -37493,7 +37493,7 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>129.0000000000055</v>
       </c>
       <c r="F37" t="n">
         <v>129.0000000000055</v>
@@ -37511,37 +37511,37 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
         <v>129.0000000000055</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>108.7860612807511</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
       <c r="U37" t="n">
-        <v>129.0000000000055</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
         <v>0</v>
@@ -37553,7 +37553,7 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>123.7878787878623</v>
       </c>
     </row>
     <row r="38">
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="L39" t="n">
+        <v>123.7878787878514</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
         <v>129.0000000000091</v>
       </c>
-      <c r="M39" t="n">
-        <v>129.0000000000091</v>
-      </c>
-      <c r="N39" t="n">
-        <v>123.7878787878514</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37724,7 +37724,7 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>129.0000000000091</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -37733,13 +37733,13 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>129.0000000000091</v>
+        <v>50.00216697636401</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>129.0000000000091</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
@@ -37772,7 +37772,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>108.7860612807511</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -37787,7 +37787,7 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>29.78822825710603</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>129.0000000000091</v>
@@ -37830,10 +37830,10 @@
         <v>129</v>
       </c>
       <c r="L41" t="n">
-        <v>124.3427939698492</v>
+        <v>129</v>
       </c>
       <c r="M41" t="n">
-        <v>50.08193525075798</v>
+        <v>45.42472922060724</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -37909,19 +37909,19 @@
         <v>129.0000000000164</v>
       </c>
       <c r="L42" t="n">
+        <v>123.7878787878296</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
         <v>129.0000000000164</v>
       </c>
-      <c r="M42" t="n">
+      <c r="P42" t="n">
         <v>129.0000000000164</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>123.7878787878296</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,13 +38064,13 @@
         <v>31.8323907398343</v>
       </c>
       <c r="K44" t="n">
-        <v>100.2288844221106</v>
+        <v>125</v>
       </c>
       <c r="L44" t="n">
-        <v>124.3427939698492</v>
+        <v>124.3427939698493</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>38.24355141237417</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -38079,10 +38079,10 @@
         <v>62.51110530027941</v>
       </c>
       <c r="P44" t="n">
-        <v>125.0000000000355</v>
+        <v>113.0196535271578</v>
       </c>
       <c r="Q44" t="n">
-        <v>51.03432051738594</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,10 +38143,10 @@
         <v>125</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>119.9494949494949</v>
       </c>
       <c r="L45" t="n">
-        <v>119.9494949494949</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
